--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Vital Signs, ResourceType Observation</t>
+    <t>This StructureDefinition contains the maps for VistA GMRV VITAL MEASUREMENT (file 120.5) to FHIR Observation</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1192,7 +1192,7 @@
     <t>FiveWs.actor</t>
   </si>
   <si>
-    <t>1619: reference from GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (#120.5-.05)</t>
+    <t>++: reference from GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (#120.5-.05)</t>
   </si>
   <si>
     <t>Observation.value[x]</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3663" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3661" uniqueCount="612">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1511,13 +1511,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://va.gov/fhir/ValueSet/VFVitalsSite</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1550,10 +1544,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>Methods for simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://va.gov/fhir/ValueSet/VFVitalsMethod</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1596,7 +1587,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/VitalSignsDevice)
 </t>
   </si>
   <si>
@@ -1621,7 +1612,7 @@
     <t>424226004 |Using device|</t>
   </si>
   <si>
-    <t>663: terminologyMaps using VF_VitalsDevice on GMRV VITAL MEASUREMENT - QUALIFIER (#120.5-5)</t>
+    <t>++: reference from GMRV VITAL MEASUREMENT – QUALIFIER &gt; GMRV VITAL QUALIFIER – VUID (#120.5-5 &gt; 120.52-99.99)</t>
   </si>
   <si>
     <t>Observation.referenceRange</t>
@@ -1757,6 +1748,9 @@
   </si>
   <si>
     <t>Need to be able to identify the target population for proper interpretation.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Codes identifying the population the reference range applies to.</t>
@@ -10590,13 +10584,11 @@
         <v>40</v>
       </c>
       <c r="X66" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="Y66" s="2"/>
+      <c r="Z66" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>40</v>
@@ -10632,33 +10624,33 @@
         <v>40</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP66" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AQ66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR66" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AQ66" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AR66" t="s" s="2">
-        <v>486</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10684,16 +10676,16 @@
         <v>139</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>40</v>
@@ -10718,13 +10710,11 @@
         <v>40</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>40</v>
@@ -10742,7 +10732,7 @@
         <v>40</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>38</v>
@@ -10763,10 +10753,10 @@
         <v>40</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>40</v>
@@ -10778,15 +10768,15 @@
         <v>40</v>
       </c>
       <c r="AR67" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10809,16 +10799,16 @@
         <v>40</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10868,7 +10858,7 @@
         <v>40</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>38</v>
@@ -10886,19 +10876,19 @@
         <v>40</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>40</v>
@@ -10909,10 +10899,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10935,16 +10925,16 @@
         <v>40</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10994,7 +10984,7 @@
         <v>40</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>38</v>
@@ -11012,33 +11002,33 @@
         <v>40</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AQ69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR69" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="AQ69" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AR69" t="s" s="2">
-        <v>515</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11061,19 +11051,19 @@
         <v>40</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>40</v>
@@ -11122,7 +11112,7 @@
         <v>40</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>38</v>
@@ -11134,7 +11124,7 @@
         <v>40</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>40</v>
@@ -11143,10 +11133,10 @@
         <v>40</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>40</v>
@@ -11163,10 +11153,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11287,10 +11277,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11413,14 +11403,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11442,10 +11432,10 @@
         <v>96</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>99</v>
@@ -11500,7 +11490,7 @@
         <v>40</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>38</v>
@@ -11541,10 +11531,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11567,13 +11557,13 @@
         <v>40</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11624,7 +11614,7 @@
         <v>40</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>38</v>
@@ -11633,7 +11623,7 @@
         <v>50</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>62</v>
@@ -11645,10 +11635,10 @@
         <v>40</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>40</v>
@@ -11665,10 +11655,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11691,13 +11681,13 @@
         <v>40</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11748,7 +11738,7 @@
         <v>40</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>38</v>
@@ -11757,7 +11747,7 @@
         <v>50</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>62</v>
@@ -11769,10 +11759,10 @@
         <v>40</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>40</v>
@@ -11789,10 +11779,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11818,16 +11808,16 @@
         <v>139</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="O76" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>40</v>
@@ -11855,10 +11845,10 @@
         <v>74</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>40</v>
@@ -11876,7 +11866,7 @@
         <v>40</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>38</v>
@@ -11894,10 +11884,10 @@
         <v>40</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>465</v>
@@ -11917,10 +11907,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11946,16 +11936,16 @@
         <v>139</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="O77" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>40</v>
@@ -11980,13 +11970,13 @@
         <v>40</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>479</v>
+        <v>554</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>40</v>
@@ -12004,7 +11994,7 @@
         <v>40</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>38</v>
@@ -12022,10 +12012,10 @@
         <v>40</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>465</v>
@@ -12045,10 +12035,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12071,17 +12061,17 @@
         <v>40</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>40</v>
@@ -12130,7 +12120,7 @@
         <v>40</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>38</v>
@@ -12154,7 +12144,7 @@
         <v>40</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>40</v>
@@ -12171,10 +12161,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12200,10 +12190,10 @@
         <v>117</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12254,7 +12244,7 @@
         <v>40</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>38</v>
@@ -12275,10 +12265,10 @@
         <v>40</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>40</v>
@@ -12295,10 +12285,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12321,16 +12311,16 @@
         <v>51</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12380,7 +12370,7 @@
         <v>40</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>38</v>
@@ -12401,10 +12391,10 @@
         <v>40</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>40</v>
@@ -12421,10 +12411,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12447,16 +12437,16 @@
         <v>51</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12506,7 +12496,7 @@
         <v>40</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>38</v>
@@ -12527,10 +12517,10 @@
         <v>40</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>40</v>
@@ -12547,10 +12537,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12573,19 +12563,19 @@
         <v>51</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>40</v>
@@ -12634,7 +12624,7 @@
         <v>40</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>38</v>
@@ -12646,19 +12636,19 @@
         <v>40</v>
       </c>
       <c r="AJ82" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>40</v>
@@ -12675,10 +12665,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12799,10 +12789,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12925,14 +12915,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12954,10 +12944,10 @@
         <v>96</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>99</v>
@@ -13012,7 +13002,7 @@
         <v>40</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>38</v>
@@ -13053,10 +13043,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13082,16 +13072,16 @@
         <v>139</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="N86" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>40</v>
@@ -13140,7 +13130,7 @@
         <v>40</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>50</v>
@@ -13158,7 +13148,7 @@
         <v>40</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>307</v>
@@ -13181,10 +13171,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13210,13 +13200,13 @@
         <v>379</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="N87" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="O87" t="s" s="2">
         <v>383</v>
@@ -13268,7 +13258,7 @@
         <v>40</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>38</v>
@@ -13277,7 +13267,7 @@
         <v>50</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>62</v>
@@ -13286,7 +13276,7 @@
         <v>40</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>388</v>
@@ -13309,10 +13299,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13338,13 +13328,13 @@
         <v>139</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="O88" t="s" s="2">
         <v>450</v>
@@ -13396,7 +13386,7 @@
         <v>40</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>38</v>
@@ -13405,7 +13395,7 @@
         <v>50</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>62</v>
@@ -13437,10 +13427,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13524,7 +13514,7 @@
         <v>40</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>38</v>
@@ -13565,10 +13555,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13594,16 +13584,16 @@
         <v>41</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>40</v>
@@ -13652,7 +13642,7 @@
         <v>40</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>38</v>
@@ -13673,10 +13663,10 @@
         <v>40</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>40</v>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3705" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3705" uniqueCount="657">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -255,10 +255,10 @@
     <t>Mapping: SNOMED CT Attribute Binding</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -943,6 +943,10 @@
     <t>Coding.code</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-30:658: fixed value "vital-signs" {null}</t>
+  </si>
+  <si>
     <t>C*E.1</t>
   </si>
   <si>
@@ -1258,13 +1262,13 @@
 </t>
   </si>
   <si>
+    <t>657: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS TAKEN (#120.5-.01)</t>
+  </si>
+  <si>
     <t>Vital.VitalSign.VitalSignTakenDateTime
 Vital.VitalSignQualifier.VitalSignTakenDateTime</t>
   </si>
   <si>
-    <t>657: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS TAKEN (#120.5-.01)</t>
-  </si>
-  <si>
     <t>Observation.issued</t>
   </si>
   <si>
@@ -1290,10 +1294,10 @@
     <t>FiveWs.recorded</t>
   </si>
   <si>
+    <t>652: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS ENTERED (#120.5-.04)</t>
+  </si>
+  <si>
     <t>Vital.VitalSign.VitalSignEnteredDateTime</t>
-  </si>
-  <si>
-    <t>652: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS ENTERED (#120.5-.04)</t>
   </si>
   <si>
     <t>Observation.performer</t>
@@ -1419,15 +1423,15 @@
   </si>
   <si>
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
+  </si>
+  <si>
+    <t>664: source value from GMRV VITAL MEASUREMENT - RATE (#120.5-1.2) case VUID not = 4500634</t>
   </si>
   <si>
     <t>Vital.VitalSign.Diastolic
 Vital.VitalSign.Systolic
 Vital.VitalSign.VitalResult
 Vital.VitalSign.VitalResultNumeric</t>
-  </si>
-  <si>
-    <t>664: source value from GMRV VITAL MEASUREMENT - RATE (#120.5-1.2) case VUID not = 4500634</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity.comparator</t>
@@ -2422,8 +2426,8 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="44.85546875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="117.9140625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="117.9140625" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="44.85546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4574,10 +4578,10 @@
         <v>84</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>210</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -5202,10 +5206,10 @@
         <v>84</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>84</v>
+        <v>255</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>255</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" hidden="true">
@@ -6315,7 +6319,7 @@
         <v>84</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>106</v>
+        <v>299</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>84</v>
@@ -6324,10 +6328,10 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>84</v>
@@ -6336,18 +6340,18 @@
         <v>84</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>84</v>
+        <v>302</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>301</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6373,14 +6377,14 @@
         <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6429,7 +6433,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6450,10 +6454,10 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>84</v>
@@ -6470,10 +6474,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6496,19 +6500,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6557,7 +6561,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6578,10 +6582,10 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>84</v>
@@ -6598,10 +6602,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6627,16 +6631,16 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6685,7 +6689,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6706,10 +6710,10 @@
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>84</v>
@@ -6726,13 +6730,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>256</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>84</v>
@@ -6856,7 +6860,7 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>266</v>
@@ -6980,7 +6984,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>267</v>
@@ -7106,7 +7110,7 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>268</v>
@@ -7234,7 +7238,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>277</v>
@@ -7358,7 +7362,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>278</v>
@@ -7484,7 +7488,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>279</v>
@@ -7529,7 +7533,7 @@
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>84</v>
@@ -7612,7 +7616,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>287</v>
@@ -7738,7 +7742,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>294</v>
@@ -7781,7 +7785,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>84</v>
@@ -7844,10 +7848,10 @@
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>84</v>
@@ -7864,10 +7868,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7893,14 +7897,14 @@
         <v>161</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7949,7 +7953,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7970,10 +7974,10 @@
         <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
@@ -7990,10 +7994,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8016,19 +8020,19 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8077,7 +8081,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8098,10 +8102,10 @@
         <v>84</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
@@ -8118,10 +8122,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8147,16 +8151,16 @@
         <v>161</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8205,7 +8209,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8226,10 +8230,10 @@
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
@@ -8246,14 +8250,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -8275,16 +8279,16 @@
         <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8312,10 +8316,10 @@
         <v>188</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -8333,7 +8337,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>94</v>
@@ -8348,22 +8352,22 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8374,10 +8378,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8400,19 +8404,19 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8461,7 +8465,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8476,36 +8480,36 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>84</v>
+        <v>366</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>365</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8528,16 +8532,16 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8587,7 +8591,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8608,13 +8612,13 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>84</v>
@@ -8628,14 +8632,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8654,19 +8658,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8715,7 +8719,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8730,19 +8734,19 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>84</v>
@@ -8756,14 +8760,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8782,19 +8786,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8831,7 +8835,7 @@
         <v>84</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
@@ -8841,7 +8845,7 @@
         <v>170</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8850,25 +8854,25 @@
         <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>84</v>
@@ -8882,16 +8886,16 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8910,19 +8914,19 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8971,7 +8975,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8980,42 +8984,42 @@
         <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9038,16 +9042,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9097,7 +9101,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9118,30 +9122,30 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9164,17 +9168,17 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9223,7 +9227,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9238,36 +9242,36 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>84</v>
+        <v>422</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>421</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9290,19 +9294,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9330,16 +9334,16 @@
         <v>188</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
@@ -9349,7 +9353,7 @@
         <v>170</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9358,7 +9362,7 @@
         <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>106</v>
@@ -9367,19 +9371,19 @@
         <v>84</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9390,13 +9394,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>84</v>
@@ -9418,19 +9422,19 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9458,10 +9462,10 @@
         <v>188</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -9479,7 +9483,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9488,7 +9492,7 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9497,19 +9501,19 @@
         <v>84</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9520,10 +9524,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9644,10 +9648,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9770,10 +9774,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9796,19 +9800,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9857,7 +9861,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9878,10 +9882,10 @@
         <v>84</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>84</v>
@@ -9890,18 +9894,18 @@
         <v>84</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9927,20 +9931,20 @@
         <v>114</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q60" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="R60" t="s" s="2">
         <v>84</v>
@@ -9964,10 +9968,10 @@
         <v>177</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>84</v>
@@ -9985,7 +9989,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10006,10 +10010,10 @@
         <v>84</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>84</v>
@@ -10026,10 +10030,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10055,14 +10059,14 @@
         <v>161</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -10111,7 +10115,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10132,10 +10136,10 @@
         <v>84</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>84</v>
@@ -10152,10 +10156,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10181,14 +10185,14 @@
         <v>108</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -10237,7 +10241,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10246,7 +10250,7 @@
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -10258,10 +10262,10 @@
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>84</v>
@@ -10278,10 +10282,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10307,16 +10311,16 @@
         <v>114</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10365,7 +10369,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10386,10 +10390,10 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>
@@ -10398,18 +10402,18 @@
         <v>84</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>84</v>
+        <v>490</v>
       </c>
       <c r="AR63" t="s" s="2">
-        <v>489</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10435,16 +10439,16 @@
         <v>183</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10472,10 +10476,10 @@
         <v>188</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
@@ -10493,7 +10497,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10502,7 +10506,7 @@
         <v>94</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>106</v>
@@ -10517,7 +10521,7 @@
         <v>137</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>84</v>
@@ -10534,14 +10538,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10563,16 +10567,16 @@
         <v>183</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10600,10 +10604,10 @@
         <v>188</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -10621,7 +10625,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10639,19 +10643,19 @@
         <v>84</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10662,10 +10666,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10688,19 +10692,19 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -10749,7 +10753,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10770,10 +10774,10 @@
         <v>84</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>84</v>
@@ -10790,10 +10794,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10819,13 +10823,13 @@
         <v>183</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10855,7 +10859,7 @@
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
@@ -10873,7 +10877,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10891,33 +10895,33 @@
         <v>84</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>84</v>
+        <v>529</v>
       </c>
       <c r="AR67" t="s" s="2">
-        <v>528</v>
+        <v>84</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10943,16 +10947,16 @@
         <v>183</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -10981,7 +10985,7 @@
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>84</v>
@@ -10999,7 +11003,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11020,10 +11024,10 @@
         <v>84</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>84</v>
@@ -11032,18 +11036,18 @@
         <v>84</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>84</v>
+        <v>538</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>537</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11066,16 +11070,16 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11125,7 +11129,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11143,19 +11147,19 @@
         <v>84</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11166,10 +11170,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11192,16 +11196,16 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -11251,7 +11255,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11269,33 +11273,33 @@
         <v>84</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>84</v>
+        <v>557</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>556</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11318,19 +11322,19 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11379,7 +11383,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11391,7 +11395,7 @@
         <v>84</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>84</v>
@@ -11400,10 +11404,10 @@
         <v>84</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>84</v>
@@ -11420,10 +11424,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11544,10 +11548,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11670,14 +11674,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11699,10 +11703,10 @@
         <v>140</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>143</v>
@@ -11757,7 +11761,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11798,10 +11802,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11824,13 +11828,13 @@
         <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11881,7 +11885,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11890,7 +11894,7 @@
         <v>94</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>106</v>
@@ -11902,10 +11906,10 @@
         <v>84</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>84</v>
@@ -11922,10 +11926,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11948,13 +11952,13 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -12005,7 +12009,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12014,7 +12018,7 @@
         <v>94</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>106</v>
@@ -12026,10 +12030,10 @@
         <v>84</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>84</v>
@@ -12046,10 +12050,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12075,16 +12079,16 @@
         <v>183</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12112,10 +12116,10 @@
         <v>118</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>84</v>
@@ -12133,7 +12137,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12151,13 +12155,13 @@
         <v>84</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>84</v>
@@ -12174,10 +12178,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12203,16 +12207,16 @@
         <v>183</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12237,13 +12241,13 @@
         <v>84</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
@@ -12261,7 +12265,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12279,13 +12283,13 @@
         <v>84</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>84</v>
@@ -12302,10 +12306,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12328,17 +12332,17 @@
         <v>84</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -12387,7 +12391,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12411,7 +12415,7 @@
         <v>84</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>84</v>
@@ -12428,10 +12432,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12457,10 +12461,10 @@
         <v>161</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12511,7 +12515,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12532,10 +12536,10 @@
         <v>84</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>84</v>
@@ -12552,10 +12556,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12578,16 +12582,16 @@
         <v>95</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12637,7 +12641,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12658,10 +12662,10 @@
         <v>84</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>84</v>
@@ -12678,10 +12682,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12704,16 +12708,16 @@
         <v>95</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12763,7 +12767,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12784,10 +12788,10 @@
         <v>84</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>84</v>
@@ -12804,10 +12808,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12830,19 +12834,19 @@
         <v>95</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>84</v>
@@ -12891,7 +12895,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -12903,7 +12907,7 @@
         <v>84</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>84</v>
@@ -12912,10 +12916,10 @@
         <v>84</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>84</v>
@@ -12932,10 +12936,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13056,10 +13060,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13182,14 +13186,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -13211,10 +13215,10 @@
         <v>140</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>143</v>
@@ -13269,7 +13273,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13310,10 +13314,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13339,16 +13343,16 @@
         <v>183</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>84</v>
@@ -13376,10 +13380,10 @@
         <v>188</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>84</v>
@@ -13397,7 +13401,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>94</v>
@@ -13415,16 +13419,16 @@
         <v>84</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>84</v>
@@ -13438,10 +13442,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13464,19 +13468,19 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>84</v>
@@ -13504,10 +13508,10 @@
         <v>188</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>84</v>
@@ -13525,7 +13529,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13534,7 +13538,7 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>106</v>
@@ -13543,19 +13547,19 @@
         <v>84</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -13566,10 +13570,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13595,16 +13599,16 @@
         <v>183</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
@@ -13632,10 +13636,10 @@
         <v>188</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>84</v>
@@ -13653,7 +13657,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13662,7 +13666,7 @@
         <v>94</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>106</v>
@@ -13677,7 +13681,7 @@
         <v>137</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>84</v>
@@ -13694,14 +13698,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13723,16 +13727,16 @@
         <v>183</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>84</v>
@@ -13760,10 +13764,10 @@
         <v>188</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>84</v>
@@ -13781,7 +13785,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13799,19 +13803,19 @@
         <v>84</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
@@ -13822,10 +13826,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13851,16 +13855,16 @@
         <v>85</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>84</v>
@@ -13909,7 +13913,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -13930,10 +13934,10 @@
         <v>84</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -944,7 +944,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-30:658: fixed value "vital-signs" {null}</t>
+inv-36:658: fixed value = vital-signs {null}</t>
   </si>
   <si>
     <t>C*E.1</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -944,7 +944,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-36:658: fixed value = vital-signs {null}</t>
+inv-34:658: fixed value = vital-signs {null}</t>
   </si>
   <si>
     <t>C*E.1</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -944,7 +944,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-34:658: fixed value = vital-signs {null}</t>
+inv-36:658: fixed value = vital-signs {null}</t>
   </si>
   <si>
     <t>C*E.1</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -944,7 +944,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-36:658: fixed value = vital-signs {null}</t>
+inv-37:658: fixed value = vital-signs {null}</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1328,7 +1328,7 @@
     <t>FiveWs.actor</t>
   </si>
   <si>
-    <t>++: reference from GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (#120.5-.05)</t>
+    <t>1653: reference from GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (#120.5-.05)</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -1748,7 +1748,7 @@
     <t>424226004 |Using device|</t>
   </si>
   <si>
-    <t>++: reference from GMRV VITAL MEASUREMENT – QUALIFIER &gt; GMRV VITAL QUALIFIER – VUID (#120.5-5 &gt; 120.52-99.99)</t>
+    <t>1655: reference from GMRV VITAL MEASUREMENT – QUALIFIER &gt; GMRV VITAL QUALIFIER – VUID (#120.5-5 &gt; 120.52-99.99)</t>
   </si>
   <si>
     <t>Observation.referenceRange</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -809,7 +809,7 @@
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>656: transform using "entered-in-error" on GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (#120.5-4) case not null</t>
+    <t>656: transform using #entered-in-error on GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (#120.5-4) case not null</t>
   </si>
   <si>
     <t>Observation.category</t>
@@ -2426,7 +2426,7 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="117.9140625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="117.765625" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="44.85546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA GMRV VITAL MEASUREMENT (file 120.5) to FHIR Observation</t>
+    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (#120.5) to us-core-vital-signs</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3705" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3705" uniqueCount="656">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Vital Signs {Observation}</t>
+    <t>Vital Signs Observation</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -941,10 +941,6 @@
   </si>
   <si>
     <t>Coding.code</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-37:658: fixed value = vital-signs {null}</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -4477,7 +4473,7 @@
         <v>94</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>84</v>
@@ -6239,7 +6235,7 @@
         <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>84</v>
@@ -6319,28 +6315,28 @@
         <v>84</v>
       </c>
       <c r="AJ31" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AK31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ31" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6348,10 +6344,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6377,14 +6373,14 @@
         <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6433,7 +6429,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6454,10 +6450,10 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>84</v>
@@ -6474,10 +6470,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6500,19 +6496,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6561,7 +6557,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6582,10 +6578,10 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>84</v>
@@ -6602,10 +6598,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6631,16 +6627,16 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6689,7 +6685,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6710,10 +6706,10 @@
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>84</v>
@@ -6730,13 +6726,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>256</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>84</v>
@@ -6860,7 +6856,7 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>266</v>
@@ -6984,7 +6980,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>267</v>
@@ -7110,7 +7106,7 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>268</v>
@@ -7238,7 +7234,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>277</v>
@@ -7362,7 +7358,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>278</v>
@@ -7488,7 +7484,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>279</v>
@@ -7533,7 +7529,7 @@
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>84</v>
@@ -7616,7 +7612,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>287</v>
@@ -7742,7 +7738,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>294</v>
@@ -7785,7 +7781,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>84</v>
@@ -7848,10 +7844,10 @@
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>84</v>
@@ -7868,10 +7864,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7897,14 +7893,14 @@
         <v>161</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7953,7 +7949,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7974,10 +7970,10 @@
         <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
@@ -7994,10 +7990,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8020,19 +8016,19 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8081,7 +8077,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8102,10 +8098,10 @@
         <v>84</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
@@ -8122,10 +8118,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8151,16 +8147,16 @@
         <v>161</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8209,7 +8205,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8230,10 +8226,10 @@
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
@@ -8250,14 +8246,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -8279,16 +8275,16 @@
         <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8316,11 +8312,11 @@
         <v>188</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>349</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
       </c>
@@ -8337,7 +8333,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>94</v>
@@ -8352,22 +8348,22 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AL47" t="s" s="2">
+      <c r="AM47" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AO47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8378,10 +8374,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8404,19 +8400,19 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8465,7 +8461,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8480,25 +8476,25 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="AL48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AO48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ48" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>84</v>
@@ -8506,10 +8502,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8532,16 +8528,16 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8591,7 +8587,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8612,13 +8608,13 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>84</v>
@@ -8632,14 +8628,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8658,19 +8654,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8719,7 +8715,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8734,19 +8730,19 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>84</v>
@@ -8760,14 +8756,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8786,19 +8782,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8835,7 +8831,7 @@
         <v>84</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
@@ -8845,7 +8841,7 @@
         <v>170</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8854,25 +8850,25 @@
         <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AJ51" t="s" s="2">
+      <c r="AK51" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AK51" t="s" s="2">
+      <c r="AL51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AL51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>84</v>
@@ -8886,16 +8882,16 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C52" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="B52" t="s" s="2">
+      <c r="D52" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="D52" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8914,19 +8910,19 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8975,7 +8971,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8984,42 +8980,42 @@
         <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AJ52" t="s" s="2">
+      <c r="AK52" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AK52" t="s" s="2">
+      <c r="AL52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AO52" t="s" s="2">
-        <v>397</v>
-      </c>
       <c r="AP52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ52" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AR52" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AR52" t="s" s="2">
-        <v>402</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9033,7 +9029,7 @@
         <v>94</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>84</v>
@@ -9042,16 +9038,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9101,7 +9097,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9122,30 +9118,30 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AO53" t="s" s="2">
+      <c r="AP53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ53" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AP53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ53" t="s" s="2">
+      <c r="AR53" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AR53" t="s" s="2">
-        <v>412</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9159,7 +9155,7 @@
         <v>83</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>84</v>
@@ -9168,17 +9164,17 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9227,7 +9223,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9242,25 +9238,25 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AL54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AO54" t="s" s="2">
+      <c r="AP54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ54" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ54" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>84</v>
@@ -9268,10 +9264,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9294,19 +9290,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9334,16 +9330,16 @@
         <v>188</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>430</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
@@ -9353,7 +9349,7 @@
         <v>170</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9362,7 +9358,7 @@
         <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>106</v>
@@ -9371,19 +9367,19 @@
         <v>84</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9394,13 +9390,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="C56" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>84</v>
@@ -9422,19 +9418,19 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9462,11 +9458,11 @@
         <v>188</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="Z56" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="Z56" t="s" s="2">
-        <v>430</v>
-      </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
       </c>
@@ -9483,7 +9479,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9492,7 +9488,7 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9501,19 +9497,19 @@
         <v>84</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9524,10 +9520,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B57" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9648,10 +9644,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9774,10 +9770,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B59" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9791,7 +9787,7 @@
         <v>94</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>84</v>
@@ -9800,19 +9796,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9861,7 +9857,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9882,30 +9878,30 @@
         <v>84</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AO59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
+      <c r="AR59" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AR59" t="s" s="2">
-        <v>454</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9931,20 +9927,20 @@
         <v>114</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q60" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="P60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q60" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="R60" t="s" s="2">
         <v>84</v>
@@ -9968,28 +9964,28 @@
         <v>177</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="Z60" t="s" s="2">
+      <c r="AA60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10010,10 +10006,10 @@
         <v>84</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>84</v>
@@ -10030,10 +10026,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10059,14 +10055,14 @@
         <v>161</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -10115,7 +10111,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10136,10 +10132,10 @@
         <v>84</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>84</v>
@@ -10156,10 +10152,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10185,14 +10181,14 @@
         <v>108</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -10241,7 +10237,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10250,7 +10246,7 @@
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -10262,10 +10258,10 @@
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>84</v>
@@ -10282,10 +10278,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10299,7 +10295,7 @@
         <v>94</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>84</v>
@@ -10311,16 +10307,16 @@
         <v>114</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10369,7 +10365,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10390,19 +10386,19 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AN63" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ63" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>84</v>
@@ -10410,10 +10406,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10439,16 +10435,16 @@
         <v>183</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10476,11 +10472,11 @@
         <v>188</v>
       </c>
       <c r="Y64" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="Z64" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="Z64" t="s" s="2">
-        <v>497</v>
-      </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
       </c>
@@ -10497,7 +10493,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10506,7 +10502,7 @@
         <v>94</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>106</v>
@@ -10521,7 +10517,7 @@
         <v>137</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>84</v>
@@ -10538,14 +10534,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10567,16 +10563,16 @@
         <v>183</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10604,11 +10600,11 @@
         <v>188</v>
       </c>
       <c r="Y65" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="Z65" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="Z65" t="s" s="2">
-        <v>507</v>
-      </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
       </c>
@@ -10625,7 +10621,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10643,19 +10639,19 @@
         <v>84</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AM65" t="s" s="2">
+      <c r="AN65" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10666,10 +10662,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10692,19 +10688,19 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -10753,7 +10749,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10774,10 +10770,10 @@
         <v>84</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>84</v>
@@ -10794,10 +10790,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10811,7 +10807,7 @@
         <v>94</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>84</v>
@@ -10823,13 +10819,13 @@
         <v>183</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10859,7 +10855,7 @@
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
@@ -10877,7 +10873,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10895,22 +10891,22 @@
         <v>84</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AN67" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="AO67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP67" t="s" s="2">
+      <c r="AQ67" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="AQ67" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>84</v>
@@ -10918,10 +10914,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10935,7 +10931,7 @@
         <v>94</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>84</v>
@@ -10947,16 +10943,16 @@
         <v>183</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -10985,7 +10981,7 @@
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>84</v>
@@ -11003,7 +10999,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11024,19 +11020,19 @@
         <v>84</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>84</v>
@@ -11044,10 +11040,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11070,16 +11066,16 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11129,7 +11125,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11147,19 +11143,19 @@
         <v>84</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AN69" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11170,10 +11166,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11187,7 +11183,7 @@
         <v>94</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>84</v>
@@ -11196,16 +11192,16 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -11255,7 +11251,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11273,22 +11269,22 @@
         <v>84</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="AN70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="AO70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP70" t="s" s="2">
+      <c r="AQ70" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>84</v>
@@ -11296,10 +11292,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11322,19 +11318,19 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11383,7 +11379,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11395,19 +11391,19 @@
         <v>84</v>
       </c>
       <c r="AJ71" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="AK71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AN71" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>84</v>
@@ -11424,10 +11420,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11548,10 +11544,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11674,14 +11670,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11703,10 +11699,10 @@
         <v>140</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>143</v>
@@ -11761,7 +11757,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11802,10 +11798,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11828,13 +11824,13 @@
         <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11885,7 +11881,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11894,7 +11890,7 @@
         <v>94</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>106</v>
@@ -11906,10 +11902,10 @@
         <v>84</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>84</v>
@@ -11926,10 +11922,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11952,13 +11948,13 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -12009,7 +12005,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12018,7 +12014,7 @@
         <v>94</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>106</v>
@@ -12030,10 +12026,10 @@
         <v>84</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>84</v>
@@ -12050,10 +12046,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12079,16 +12075,16 @@
         <v>183</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12116,11 +12112,11 @@
         <v>118</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="Z77" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="Z77" t="s" s="2">
-        <v>591</v>
-      </c>
       <c r="AA77" t="s" s="2">
         <v>84</v>
       </c>
@@ -12137,7 +12133,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12155,13 +12151,13 @@
         <v>84</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="AM77" t="s" s="2">
-        <v>593</v>
-      </c>
       <c r="AN77" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>84</v>
@@ -12178,10 +12174,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12207,16 +12203,16 @@
         <v>183</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12241,14 +12237,14 @@
         <v>84</v>
       </c>
       <c r="X78" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="Y78" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="Y78" t="s" s="2">
+      <c r="Z78" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="Z78" t="s" s="2">
-        <v>601</v>
-      </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
       </c>
@@ -12265,7 +12261,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12283,13 +12279,13 @@
         <v>84</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="AM78" t="s" s="2">
-        <v>593</v>
-      </c>
       <c r="AN78" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>84</v>
@@ -12306,10 +12302,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12332,17 +12328,17 @@
         <v>84</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -12391,7 +12387,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12415,7 +12411,7 @@
         <v>84</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>84</v>
@@ -12432,10 +12428,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12461,10 +12457,10 @@
         <v>161</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12515,7 +12511,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12536,10 +12532,10 @@
         <v>84</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>84</v>
@@ -12556,10 +12552,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12582,16 +12578,16 @@
         <v>95</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12641,7 +12637,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12662,10 +12658,10 @@
         <v>84</v>
       </c>
       <c r="AM81" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>84</v>
@@ -12682,10 +12678,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12708,16 +12704,16 @@
         <v>95</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12767,7 +12763,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12788,10 +12784,10 @@
         <v>84</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>84</v>
@@ -12808,10 +12804,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12834,19 +12830,19 @@
         <v>95</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>84</v>
@@ -12895,7 +12891,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -12907,19 +12903,19 @@
         <v>84</v>
       </c>
       <c r="AJ83" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM83" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="AK83" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM83" t="s" s="2">
+      <c r="AN83" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>84</v>
@@ -12936,10 +12932,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13060,10 +13056,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13186,14 +13182,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -13215,10 +13211,10 @@
         <v>140</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>143</v>
@@ -13273,7 +13269,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13314,10 +13310,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13343,16 +13339,16 @@
         <v>183</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="N87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>84</v>
@@ -13380,11 +13376,11 @@
         <v>188</v>
       </c>
       <c r="Y87" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="Z87" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="Z87" t="s" s="2">
-        <v>349</v>
-      </c>
       <c r="AA87" t="s" s="2">
         <v>84</v>
       </c>
@@ -13401,7 +13397,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>94</v>
@@ -13419,16 +13415,16 @@
         <v>84</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AM87" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AN87" t="s" s="2">
+      <c r="AO87" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>84</v>
@@ -13442,10 +13438,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13468,19 +13464,19 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="N88" t="s" s="2">
-        <v>645</v>
-      </c>
       <c r="O88" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>84</v>
@@ -13508,11 +13504,11 @@
         <v>188</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="Z88" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="Z88" t="s" s="2">
-        <v>430</v>
-      </c>
       <c r="AA88" t="s" s="2">
         <v>84</v>
       </c>
@@ -13529,7 +13525,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13538,7 +13534,7 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>106</v>
@@ -13547,19 +13543,19 @@
         <v>84</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AN88" t="s" s="2">
+      <c r="AO88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP88" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP88" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -13570,10 +13566,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13599,16 +13595,16 @@
         <v>183</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="N89" t="s" s="2">
-        <v>651</v>
-      </c>
       <c r="O89" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
@@ -13636,11 +13632,11 @@
         <v>188</v>
       </c>
       <c r="Y89" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="Z89" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="Z89" t="s" s="2">
-        <v>497</v>
-      </c>
       <c r="AA89" t="s" s="2">
         <v>84</v>
       </c>
@@ -13657,7 +13653,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13666,7 +13662,7 @@
         <v>94</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>106</v>
@@ -13681,7 +13677,7 @@
         <v>137</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>84</v>
@@ -13698,14 +13694,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13727,16 +13723,16 @@
         <v>183</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>84</v>
@@ -13764,11 +13760,11 @@
         <v>188</v>
       </c>
       <c r="Y90" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="Z90" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="Z90" t="s" s="2">
-        <v>507</v>
-      </c>
       <c r="AA90" t="s" s="2">
         <v>84</v>
       </c>
@@ -13785,7 +13781,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13803,19 +13799,19 @@
         <v>84</v>
       </c>
       <c r="AL90" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AM90" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AM90" t="s" s="2">
+      <c r="AN90" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AN90" t="s" s="2">
+      <c r="AO90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP90" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP90" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
@@ -13826,10 +13822,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13855,16 +13851,16 @@
         <v>85</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="M91" t="s" s="2">
-        <v>656</v>
-      </c>
       <c r="N91" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="O91" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>84</v>
@@ -13913,7 +13909,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -13934,10 +13930,10 @@
         <v>84</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1744,7 +1744,7 @@
     <t>424226004 |Using device|</t>
   </si>
   <si>
-    <t>1655: reference from GMRV VITAL MEASUREMENT – QUALIFIER &gt; GMRV VITAL QUALIFIER – VUID (#120.5-5 &gt; 120.52-99.99)</t>
+    <t>1655: reference from GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (#120.5-5 &gt; 120.52-99.99)</t>
   </si>
   <si>
     <t>Observation.referenceRange</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3705" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3706" uniqueCount="656">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -809,7 +809,7 @@
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>656: transform using #entered-in-error on GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (#120.5-4) case not null</t>
+    <t>656: transform using "entered-in-error" on GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (#120.5-4) case not null</t>
   </si>
   <si>
     <t>Observation.category</t>
@@ -1643,7 +1643,13 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsSite</t>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1656,9 +1662,6 @@
   </si>
   <si>
     <t>718497002 |Inherent location|</t>
-  </si>
-  <si>
-    <t>662: terminologyMaps using VF_VitalsSite on GMRV VITAL MEASUREMENT - QUALIFIER (#120.5-5)</t>
   </si>
   <si>
     <t>Observation.method</t>
@@ -1880,9 +1883,6 @@
   </si>
   <si>
     <t>Need to be able to identify the target population for proper interpretation.</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>Codes identifying the population the reference range applies to.</t>
@@ -2422,7 +2422,7 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="117.765625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="117.9140625" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="44.85546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -10807,7 +10807,7 @@
         <v>94</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>84</v>
@@ -10851,11 +10851,13 @@
         <v>84</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y67" s="2"/>
+        <v>523</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>524</v>
+      </c>
       <c r="Z67" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
@@ -10891,22 +10893,22 @@
         <v>84</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>528</v>
+        <v>84</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>84</v>
@@ -10914,10 +10916,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10943,16 +10945,16 @@
         <v>183</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -10981,7 +10983,7 @@
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>84</v>
@@ -10999,7 +11001,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11020,10 +11022,10 @@
         <v>84</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>84</v>
@@ -11032,7 +11034,7 @@
         <v>84</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>84</v>
@@ -11040,10 +11042,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11066,16 +11068,16 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11125,7 +11127,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11143,19 +11145,19 @@
         <v>84</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11166,10 +11168,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11192,16 +11194,16 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -11251,7 +11253,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11269,22 +11271,22 @@
         <v>84</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>84</v>
@@ -11292,10 +11294,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11318,19 +11320,19 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11379,7 +11381,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11391,7 +11393,7 @@
         <v>84</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>84</v>
@@ -11400,10 +11402,10 @@
         <v>84</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>84</v>
@@ -11420,10 +11422,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11544,10 +11546,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11670,14 +11672,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11699,10 +11701,10 @@
         <v>140</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>143</v>
@@ -11757,7 +11759,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11798,10 +11800,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11824,13 +11826,13 @@
         <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11881,7 +11883,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11890,7 +11892,7 @@
         <v>94</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>106</v>
@@ -11902,10 +11904,10 @@
         <v>84</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>84</v>
@@ -11922,10 +11924,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11948,13 +11950,13 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -12005,7 +12007,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12014,7 +12016,7 @@
         <v>94</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>106</v>
@@ -12026,10 +12028,10 @@
         <v>84</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>84</v>
@@ -12046,10 +12048,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12075,16 +12077,16 @@
         <v>183</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12112,10 +12114,10 @@
         <v>118</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>84</v>
@@ -12133,7 +12135,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12151,10 +12153,10 @@
         <v>84</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>509</v>
@@ -12174,10 +12176,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12203,16 +12205,16 @@
         <v>183</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12237,7 +12239,7 @@
         <v>84</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>598</v>
+        <v>523</v>
       </c>
       <c r="Y78" t="s" s="2">
         <v>599</v>
@@ -12261,7 +12263,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12279,10 +12281,10 @@
         <v>84</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>509</v>
@@ -12532,7 +12534,7 @@
         <v>84</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>610</v>
@@ -12830,7 +12832,7 @@
         <v>95</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L83" t="s" s="2">
         <v>625</v>
@@ -13189,7 +13191,7 @@
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -13211,10 +13213,10 @@
         <v>140</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>143</v>
@@ -13269,7 +13271,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13857,10 +13859,10 @@
         <v>655</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>84</v>
@@ -13930,10 +13932,10 @@
         <v>84</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$99</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3706" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4020" uniqueCount="693">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1537,6 +1537,120 @@
   </si>
   <si>
     <t>665: transform using VF_VitalsUnits on GMRV VITAL MEASUREMENT - VITAL TYPE (#120.5-.03)</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.code.id</t>
+  </si>
+  <si>
+    <t>Observation.value[x].code.id</t>
+  </si>
+  <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x].code.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.code.extension:11179-permitted-value-conceptmap</t>
+  </si>
+  <si>
+    <t>11179-permitted-value-conceptmap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {11179-permitted-value-conceptmap}
+</t>
+  </si>
+  <si>
+    <t>Mapping from permitted to transmitted</t>
+  </si>
+  <si>
+    <t>Expresses the linkage between the internal codes used for storage and the codes used for exchange.</t>
+  </si>
+  <si>
+    <t>The permitted value set must have a 1..1 set of codes for each code in the value meaning value set.  The source for the concept map is the value set the extension appears on.  The target is the permitted-value-valueset.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.code.extension:11179-permitted-value-conceptmap.id</t>
+  </si>
+  <si>
+    <t>Observation.value[x].code.extension.id</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.code.extension:11179-permitted-value-conceptmap.extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x].code.extension.extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.code.extension:11179-permitted-value-conceptmap.url</t>
+  </si>
+  <si>
+    <t>Observation.value[x].code.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/11179-permitted-value-conceptmap</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.code.extension:11179-permitted-value-conceptmap.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.value[x].code.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(ConceptMap)
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ConceptMap/CMVFVitalsUnits</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.code.value</t>
+  </si>
+  <si>
+    <t>Observation.value[x].code.value</t>
+  </si>
+  <si>
+    <t>Primitive value for code</t>
+  </si>
+  <si>
+    <t>string.value</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -2378,12 +2492,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR91"/>
+  <dimension ref="A1:AR99"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.29296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="91.8671875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="34.3203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -10409,7 +10523,7 @@
         <v>490</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10423,7 +10537,7 @@
         <v>94</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>84</v>
@@ -10432,20 +10546,16 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N64" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="O64" t="s" s="2">
-        <v>494</v>
-      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>84</v>
       </c>
@@ -10469,13 +10579,13 @@
         <v>84</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>495</v>
+        <v>84</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>496</v>
+        <v>84</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
@@ -10493,7 +10603,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>490</v>
+        <v>164</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10502,10 +10612,10 @@
         <v>94</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>497</v>
+        <v>84</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>84</v>
@@ -10514,10 +10624,10 @@
         <v>84</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>498</v>
+        <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>84</v>
@@ -10534,14 +10644,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>500</v>
+        <v>84</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10560,20 +10670,16 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>504</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>84</v>
       </c>
@@ -10597,31 +10703,29 @@
         <v>84</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>505</v>
+        <v>84</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>506</v>
+        <v>84</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="AC65" s="2"/>
       <c r="AD65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>499</v>
+        <v>171</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10633,25 +10737,25 @@
         <v>84</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>507</v>
+        <v>84</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>508</v>
+        <v>84</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>509</v>
+        <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>510</v>
+        <v>84</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10662,12 +10766,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="C66" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>499</v>
+      </c>
       <c r="D66" t="s" s="2">
         <v>84</v>
       </c>
@@ -10676,7 +10782,7 @@
         <v>82</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>84</v>
@@ -10688,20 +10794,18 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>516</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>84</v>
       </c>
@@ -10749,7 +10853,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>511</v>
+        <v>171</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10758,10 +10862,10 @@
         <v>83</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>84</v>
+        <v>504</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>84</v>
@@ -10770,10 +10874,10 @@
         <v>84</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>517</v>
+        <v>137</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>518</v>
+        <v>137</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>84</v>
@@ -10790,10 +10894,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>519</v>
+        <v>505</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10816,17 +10920,15 @@
         <v>84</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>520</v>
+        <v>162</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>522</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>84</v>
@@ -10851,13 +10953,13 @@
         <v>84</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>523</v>
+        <v>84</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>524</v>
+        <v>84</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>525</v>
+        <v>84</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
@@ -10875,7 +10977,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>519</v>
+        <v>164</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10887,25 +10989,25 @@
         <v>84</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>526</v>
+        <v>84</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>527</v>
+        <v>84</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>528</v>
+        <v>165</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>529</v>
+        <v>84</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -10916,10 +11018,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>530</v>
+        <v>507</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>530</v>
+        <v>508</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10930,10 +11032,10 @@
         <v>82</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>84</v>
@@ -10942,20 +11044,16 @@
         <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>531</v>
+        <v>496</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>534</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>84</v>
       </c>
@@ -10979,41 +11077,43 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y68" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z68" t="s" s="2">
-        <v>535</v>
+        <v>84</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>530</v>
+        <v>171</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>84</v>
@@ -11022,10 +11122,10 @@
         <v>84</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>536</v>
+        <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>537</v>
+        <v>84</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>84</v>
@@ -11034,7 +11134,7 @@
         <v>84</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>538</v>
+        <v>84</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>84</v>
@@ -11042,10 +11142,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>539</v>
+        <v>509</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>539</v>
+        <v>510</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11053,7 +11153,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>94</v>
@@ -11068,16 +11168,16 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>540</v>
+        <v>108</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>541</v>
+        <v>511</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>542</v>
+        <v>512</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>543</v>
+        <v>513</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11085,7 +11185,7 @@
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>84</v>
+        <v>514</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>84</v>
@@ -11127,10 +11227,10 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>539</v>
+        <v>515</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>94</v>
@@ -11139,25 +11239,25 @@
         <v>84</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>544</v>
+        <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>545</v>
+        <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>546</v>
+        <v>137</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>547</v>
+        <v>84</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11168,10 +11268,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>548</v>
+        <v>516</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>548</v>
+        <v>517</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11179,13 +11279,13 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>84</v>
@@ -11194,17 +11294,15 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>549</v>
+        <v>518</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>550</v>
+        <v>519</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>552</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11214,7 +11312,7 @@
         <v>84</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>84</v>
+        <v>521</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>84</v>
@@ -11253,7 +11351,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>548</v>
+        <v>522</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11271,22 +11369,22 @@
         <v>84</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>553</v>
+        <v>84</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>554</v>
+        <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>555</v>
+        <v>137</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>556</v>
+        <v>84</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>557</v>
+        <v>84</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>84</v>
@@ -11294,10 +11392,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>558</v>
+        <v>523</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>558</v>
+        <v>524</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11308,7 +11406,7 @@
         <v>82</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>84</v>
@@ -11320,20 +11418,16 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>559</v>
+        <v>161</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>560</v>
+        <v>525</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>563</v>
-      </c>
+        <v>525</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>84</v>
       </c>
@@ -11381,19 +11475,19 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>558</v>
+        <v>526</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>564</v>
+        <v>84</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>84</v>
@@ -11402,10 +11496,10 @@
         <v>84</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>565</v>
+        <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>566</v>
+        <v>84</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>84</v>
@@ -11422,10 +11516,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>567</v>
+        <v>527</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>567</v>
+        <v>527</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11439,7 +11533,7 @@
         <v>94</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>84</v>
@@ -11448,16 +11542,20 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>162</v>
+        <v>528</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+        <v>529</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>531</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
       </c>
@@ -11481,13 +11579,13 @@
         <v>84</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>84</v>
+        <v>532</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>84</v>
+        <v>533</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>84</v>
@@ -11505,7 +11603,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>164</v>
+        <v>527</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11514,10 +11612,10 @@
         <v>94</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>84</v>
+        <v>534</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>84</v>
@@ -11526,10 +11624,10 @@
         <v>84</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>165</v>
+        <v>535</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>84</v>
@@ -11546,14 +11644,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>568</v>
+        <v>536</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>568</v>
+        <v>536</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>139</v>
+        <v>537</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11572,18 +11670,20 @@
         <v>84</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>141</v>
+        <v>538</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>167</v>
+        <v>539</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>540</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>541</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>84</v>
       </c>
@@ -11607,13 +11707,13 @@
         <v>84</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>84</v>
+        <v>542</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>84</v>
+        <v>543</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>84</v>
@@ -11631,7 +11731,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>171</v>
+        <v>536</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11643,25 +11743,25 @@
         <v>84</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>84</v>
+        <v>544</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>84</v>
+        <v>545</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>165</v>
+        <v>546</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>84</v>
+        <v>547</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
@@ -11672,14 +11772,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>569</v>
+        <v>548</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>569</v>
+        <v>548</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>570</v>
+        <v>84</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11692,25 +11792,25 @@
         <v>84</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>140</v>
+        <v>549</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>571</v>
+        <v>550</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>572</v>
+        <v>551</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>143</v>
+        <v>552</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>149</v>
+        <v>553</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
@@ -11759,7 +11859,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>573</v>
+        <v>548</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11771,7 +11871,7 @@
         <v>84</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>84</v>
@@ -11780,10 +11880,10 @@
         <v>84</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>84</v>
+        <v>554</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>137</v>
+        <v>555</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>84</v>
@@ -11800,10 +11900,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>574</v>
+        <v>556</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>574</v>
+        <v>556</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11826,15 +11926,17 @@
         <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>575</v>
+        <v>183</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>576</v>
+        <v>557</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>558</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>559</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>84</v>
@@ -11859,13 +11961,13 @@
         <v>84</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>84</v>
+        <v>560</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>84</v>
+        <v>561</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>84</v>
+        <v>562</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>84</v>
@@ -11883,7 +11985,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>574</v>
+        <v>556</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11892,7 +11994,7 @@
         <v>94</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>578</v>
+        <v>84</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>106</v>
@@ -11901,19 +12003,19 @@
         <v>84</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>84</v>
+        <v>563</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>579</v>
+        <v>564</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>580</v>
+        <v>565</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>84</v>
+        <v>566</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
@@ -11924,10 +12026,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11941,7 +12043,7 @@
         <v>94</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>84</v>
@@ -11950,16 +12052,20 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>575</v>
+        <v>183</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>582</v>
+        <v>568</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+        <v>569</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>571</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
       </c>
@@ -11983,13 +12089,11 @@
         <v>84</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>84</v>
+        <v>572</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -12007,7 +12111,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12016,7 +12120,7 @@
         <v>94</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>578</v>
+        <v>84</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>106</v>
@@ -12028,10 +12132,10 @@
         <v>84</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>84</v>
@@ -12040,7 +12144,7 @@
         <v>84</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>84</v>
+        <v>575</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>84</v>
@@ -12048,10 +12152,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12074,20 +12178,18 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>183</v>
+        <v>577</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>589</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>84</v>
       </c>
@@ -12111,13 +12213,13 @@
         <v>84</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>590</v>
+        <v>84</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>591</v>
+        <v>84</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>84</v>
@@ -12135,7 +12237,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12153,19 +12255,19 @@
         <v>84</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>509</v>
+        <v>583</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>84</v>
+        <v>584</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12176,10 +12278,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12190,10 +12292,10 @@
         <v>82</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>84</v>
@@ -12202,20 +12304,18 @@
         <v>84</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>183</v>
+        <v>586</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>598</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>84</v>
       </c>
@@ -12239,13 +12339,13 @@
         <v>84</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>523</v>
+        <v>84</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>599</v>
+        <v>84</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>600</v>
+        <v>84</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
@@ -12263,13 +12363,13 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>84</v>
@@ -12281,22 +12381,22 @@
         <v>84</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="AM78" t="s" s="2">
+      <c r="AO78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP78" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="AN78" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AQ78" t="s" s="2">
-        <v>84</v>
+        <v>594</v>
       </c>
       <c r="AR78" t="s" s="2">
         <v>84</v>
@@ -12304,10 +12404,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12318,7 +12418,7 @@
         <v>82</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>84</v>
@@ -12330,17 +12430,19 @@
         <v>84</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>598</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>599</v>
+      </c>
       <c r="O79" t="s" s="2">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -12389,20 +12491,20 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="AG79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK79" t="s" s="2">
         <v>84</v>
       </c>
@@ -12410,10 +12512,10 @@
         <v>84</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>84</v>
+        <v>602</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>84</v>
@@ -12430,10 +12532,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12459,10 +12561,10 @@
         <v>161</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>608</v>
+        <v>162</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>609</v>
+        <v>163</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12513,7 +12615,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>607</v>
+        <v>164</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12525,7 +12627,7 @@
         <v>84</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>84</v>
@@ -12534,10 +12636,10 @@
         <v>84</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>579</v>
+        <v>84</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>610</v>
+        <v>165</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>84</v>
@@ -12554,14 +12656,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12577,19 +12679,19 @@
         <v>84</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>612</v>
+        <v>140</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>613</v>
+        <v>141</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>614</v>
+        <v>167</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>615</v>
+        <v>143</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12639,7 +12741,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>611</v>
+        <v>171</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12651,7 +12753,7 @@
         <v>84</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>84</v>
@@ -12660,10 +12762,10 @@
         <v>84</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>616</v>
+        <v>84</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>617</v>
+        <v>165</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>84</v>
@@ -12680,14 +12782,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>84</v>
+        <v>607</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12700,24 +12802,26 @@
         <v>84</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J82" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>619</v>
+        <v>140</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>84</v>
       </c>
@@ -12765,7 +12869,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12777,7 +12881,7 @@
         <v>84</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>84</v>
@@ -12786,10 +12890,10 @@
         <v>84</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>616</v>
+        <v>84</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>623</v>
+        <v>137</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>84</v>
@@ -12806,10 +12910,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>624</v>
+        <v>611</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>624</v>
+        <v>611</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12820,32 +12924,28 @@
         <v>82</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>559</v>
+        <v>612</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>628</v>
-      </c>
+        <v>614</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>84</v>
       </c>
@@ -12893,19 +12993,19 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>624</v>
+        <v>611</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>84</v>
+        <v>615</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>629</v>
+        <v>106</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>84</v>
@@ -12914,10 +13014,10 @@
         <v>84</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>630</v>
+        <v>616</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>631</v>
+        <v>617</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>84</v>
@@ -12934,10 +13034,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>632</v>
+        <v>618</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>632</v>
+        <v>618</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12960,13 +13060,13 @@
         <v>84</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>161</v>
+        <v>612</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>162</v>
+        <v>619</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>163</v>
+        <v>620</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -13017,7 +13117,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>164</v>
+        <v>618</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13026,10 +13126,10 @@
         <v>94</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>84</v>
+        <v>615</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>84</v>
@@ -13038,10 +13138,10 @@
         <v>84</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>84</v>
+        <v>616</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>165</v>
+        <v>621</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>84</v>
@@ -13058,21 +13158,21 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>633</v>
+        <v>622</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>633</v>
+        <v>622</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>84</v>
@@ -13084,18 +13184,20 @@
         <v>84</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>141</v>
+        <v>623</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>167</v>
+        <v>624</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>625</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>626</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>84</v>
       </c>
@@ -13119,13 +13221,13 @@
         <v>84</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>84</v>
+        <v>627</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>84</v>
+        <v>628</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>84</v>
@@ -13143,31 +13245,31 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>171</v>
+        <v>622</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>84</v>
+        <v>629</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>84</v>
+        <v>630</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>165</v>
+        <v>546</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>84</v>
@@ -13184,14 +13286,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>570</v>
+        <v>84</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -13204,25 +13306,25 @@
         <v>84</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>571</v>
+        <v>632</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>572</v>
+        <v>633</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>143</v>
+        <v>634</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>149</v>
+        <v>635</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>84</v>
@@ -13247,13 +13349,13 @@
         <v>84</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>84</v>
+        <v>560</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>84</v>
+        <v>636</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>84</v>
+        <v>637</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>84</v>
@@ -13271,7 +13373,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>573</v>
+        <v>631</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13283,19 +13385,19 @@
         <v>84</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>84</v>
+        <v>629</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>84</v>
+        <v>630</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>137</v>
+        <v>546</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>84</v>
@@ -13312,10 +13414,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13323,34 +13425,32 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>183</v>
+        <v>639</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>638</v>
-      </c>
+        <v>641</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>84</v>
@@ -13375,13 +13475,13 @@
         <v>84</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>347</v>
+        <v>84</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>348</v>
+        <v>84</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>84</v>
@@ -13399,10 +13499,10 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>94</v>
@@ -13417,16 +13517,16 @@
         <v>84</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>640</v>
+        <v>84</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>351</v>
+        <v>84</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>352</v>
+        <v>643</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>353</v>
+        <v>84</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>84</v>
@@ -13440,10 +13540,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13457,29 +13557,25 @@
         <v>94</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>423</v>
+        <v>161</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>646</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>84</v>
       </c>
@@ -13503,13 +13599,13 @@
         <v>84</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>428</v>
+        <v>84</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>429</v>
+        <v>84</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>84</v>
@@ -13527,7 +13623,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13536,7 +13632,7 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>645</v>
+        <v>84</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>106</v>
@@ -13545,19 +13641,19 @@
         <v>84</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>646</v>
+        <v>84</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>432</v>
+        <v>616</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>433</v>
+        <v>647</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>434</v>
+        <v>84</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -13568,10 +13664,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13582,32 +13678,30 @@
         <v>82</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J89" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="K89" t="s" s="2">
-        <v>183</v>
+        <v>649</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>494</v>
-      </c>
+        <v>652</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>84</v>
       </c>
@@ -13631,13 +13725,13 @@
         <v>84</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>495</v>
+        <v>84</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>496</v>
+        <v>84</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>84</v>
@@ -13655,16 +13749,16 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>651</v>
+        <v>84</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>106</v>
@@ -13676,10 +13770,10 @@
         <v>84</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>137</v>
+        <v>653</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>498</v>
+        <v>654</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>84</v>
@@ -13696,14 +13790,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>500</v>
+        <v>84</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13719,23 +13813,21 @@
         <v>84</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>183</v>
+        <v>656</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>501</v>
+        <v>657</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>502</v>
+        <v>658</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>504</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>84</v>
       </c>
@@ -13759,13 +13851,13 @@
         <v>84</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>505</v>
+        <v>84</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>506</v>
+        <v>84</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>84</v>
@@ -13783,7 +13875,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13801,19 +13893,19 @@
         <v>84</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>507</v>
+        <v>84</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>508</v>
+        <v>653</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>509</v>
+        <v>660</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>510</v>
+        <v>84</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
@@ -13824,10 +13916,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13841,28 +13933,28 @@
         <v>83</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>85</v>
+        <v>596</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>562</v>
+        <v>664</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>563</v>
+        <v>665</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>84</v>
@@ -13911,7 +14003,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -13923,35 +14015,1053 @@
         <v>84</v>
       </c>
       <c r="AJ91" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR91" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR92" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR93" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR94" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="P95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AK91" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP91" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ91" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR91" t="s" s="2">
+      <c r="AK95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR95" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="P96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AQ96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR96" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR97" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AQ98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR98" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="P99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR99" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR91">
+  <autoFilter ref="A1:AR99">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13961,7 +15071,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI90">
+  <conditionalFormatting sqref="A2:AI98">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -940,6 +940,9 @@
     <t>Need to refer to a particular code in the system.</t>
   </si>
   <si>
+    <t>vital-signs</t>
+  </si>
+  <si>
     <t>Coding.code</t>
   </si>
   <si>
@@ -949,7 +952,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>658: fixed value = vital-signs</t>
+    <t>658: fixed value = #vital-signs</t>
   </si>
   <si>
     <t>Observation.category.coding.display</t>
@@ -1056,9 +1059,6 @@
   </si>
   <si>
     <t>Observation.category:VSCat.coding.code</t>
-  </si>
-  <si>
-    <t>vital-signs</t>
   </si>
   <si>
     <t>Observation.category:VSCat.coding.display</t>
@@ -6378,7 +6378,7 @@
         <v>84</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>84</v>
+        <v>298</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>84</v>
@@ -6417,7 +6417,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6438,10 +6438,10 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>84</v>
@@ -6450,7 +6450,7 @@
         <v>84</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6487,14 +6487,14 @@
         <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6543,7 +6543,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6564,10 +6564,10 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>84</v>
@@ -6584,10 +6584,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6610,19 +6610,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6671,7 +6671,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6692,10 +6692,10 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>84</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6741,16 +6741,16 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6799,7 +6799,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6820,10 +6820,10 @@
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>84</v>
@@ -6840,13 +6840,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>256</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>84</v>
@@ -6970,7 +6970,7 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>266</v>
@@ -7094,7 +7094,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>267</v>
@@ -7220,7 +7220,7 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>268</v>
@@ -7348,7 +7348,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>277</v>
@@ -7472,7 +7472,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>278</v>
@@ -7598,7 +7598,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>279</v>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>84</v>
@@ -7726,7 +7726,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>287</v>
@@ -7852,7 +7852,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>294</v>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>337</v>
+        <v>298</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>84</v>
@@ -7937,7 +7937,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7958,10 +7958,10 @@
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>84</v>
@@ -7981,7 +7981,7 @@
         <v>338</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8007,14 +8007,14 @@
         <v>161</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -8063,7 +8063,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8084,10 +8084,10 @@
         <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
@@ -8107,7 +8107,7 @@
         <v>339</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8130,19 +8130,19 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8191,7 +8191,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8212,10 +8212,10 @@
         <v>84</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
@@ -8235,7 +8235,7 @@
         <v>340</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8261,16 +8261,16 @@
         <v>161</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8319,7 +8319,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8340,10 +8340,10 @@
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -809,7 +809,7 @@
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>656: transform using "entered-in-error" on GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (#120.5-4) case not null</t>
+    <t>656: transform using #entered-in-error on GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (#120.5-4) case not null</t>
   </si>
   <si>
     <t>Observation.category</t>
@@ -2536,7 +2536,7 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="117.9140625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="117.765625" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="44.85546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$92</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4020" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3738" uniqueCount="700">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -827,6 +827,14 @@
     <t>Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/observation-category"/&gt;
+    &lt;code value="vital-signs"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
@@ -843,10 +851,28 @@
     <t>FiveWs.class</t>
   </si>
   <si>
+    <t>658: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#vital-signs</t>
+  </si>
+  <si>
+    <t>Observation.category:VSCat</t>
+  </si>
+  <si>
+    <t>VSCat</t>
+  </si>
+  <si>
+    <t>Observation.category:VSCat.id</t>
+  </si>
+  <si>
     <t>Observation.category.id</t>
   </si>
   <si>
+    <t>Observation.category:VSCat.extension</t>
+  </si>
+  <si>
     <t>Observation.category.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:VSCat.coding</t>
   </si>
   <si>
     <t>Observation.category.coding</t>
@@ -877,12 +903,21 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
+    <t>Observation.category:VSCat.coding.id</t>
+  </si>
+  <si>
     <t>Observation.category.coding.id</t>
   </si>
   <si>
+    <t>Observation.category:VSCat.coding.extension</t>
+  </si>
+  <si>
     <t>Observation.category.coding.extension</t>
   </si>
   <si>
+    <t>Observation.category:VSCat.coding.system</t>
+  </si>
+  <si>
     <t>Observation.category.coding.system</t>
   </si>
   <si>
@@ -898,6 +933,9 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>http://terminology.hl7.org/CodeSystem/observation-category</t>
+  </si>
+  <si>
     <t>Coding.system</t>
   </si>
   <si>
@@ -907,6 +945,9 @@
     <t>./codeSystem</t>
   </si>
   <si>
+    <t>Observation.category:VSCat.coding.version</t>
+  </si>
+  <si>
     <t>Observation.category.coding.version</t>
   </si>
   <si>
@@ -928,6 +969,9 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
+    <t>Observation.category:VSCat.coding.code</t>
+  </si>
+  <si>
     <t>Observation.category.coding.code</t>
   </si>
   <si>
@@ -952,7 +996,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>658: fixed value = #vital-signs</t>
+    <t>Observation.category:VSCat.coding.display</t>
   </si>
   <si>
     <t>Observation.category.coding.display</t>
@@ -974,6 +1018,9 @@
   </si>
   <si>
     <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Observation.category:VSCat.coding.userSelected</t>
   </si>
   <si>
     <t>Observation.category.coding.userSelected</t>
@@ -1004,6 +1051,9 @@
     <t>CD.codingRationale</t>
   </si>
   <si>
+    <t>Observation.category:VSCat.text</t>
+  </si>
+  <si>
     <t>Observation.category.text</t>
   </si>
   <si>
@@ -1026,48 +1076,6 @@
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>Observation.category:VSCat</t>
-  </si>
-  <si>
-    <t>VSCat</t>
-  </si>
-  <si>
-    <t>Observation.category:VSCat.id</t>
-  </si>
-  <si>
-    <t>Observation.category:VSCat.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:VSCat.coding</t>
-  </si>
-  <si>
-    <t>Observation.category:VSCat.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category:VSCat.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:VSCat.coding.system</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/observation-category</t>
-  </si>
-  <si>
-    <t>Observation.category:VSCat.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.category:VSCat.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.category:VSCat.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.category:VSCat.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.category:VSCat.text</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -1111,6 +1119,24 @@
   </si>
   <si>
     <t>116680003 |Is a|</t>
+  </si>
+  <si>
+    <t>Observation.code.id</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCodes</t>
+  </si>
+  <si>
+    <t>661: terminologyMaps using VF_VitalsCodes on GMRV VITAL MEASUREMENT - VITAL TYPE (#120.5-.03)</t>
+  </si>
+  <si>
+    <t>Observation.code.text</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -2492,7 +2518,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR99"/>
+  <dimension ref="A1:AR92"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="91.8671875" customWidth="true" bestFit="true"/>
@@ -5372,7 +5398,7 @@
         <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>84</v>
+        <v>261</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>84</v>
@@ -5390,16 +5416,16 @@
         <v>118</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5433,16 +5459,16 @@
         <v>84</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>84</v>
+        <v>267</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -5450,24 +5476,26 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>84</v>
@@ -5476,16 +5504,20 @@
         <v>84</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>162</v>
+        <v>257</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
       </c>
@@ -5509,13 +5541,13 @@
         <v>84</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>84</v>
+        <v>262</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>84</v>
+        <v>263</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -5533,19 +5565,19 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>164</v>
+        <v>256</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>84</v>
@@ -5557,10 +5589,10 @@
         <v>84</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>165</v>
+        <v>265</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>84</v>
+        <v>266</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>84</v>
@@ -5574,21 +5606,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>84</v>
@@ -5600,17 +5632,15 @@
         <v>84</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5647,31 +5677,31 @@
         <v>84</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>84</v>
@@ -5700,14 +5730,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5723,23 +5753,21 @@
         <v>84</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>269</v>
+        <v>140</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>270</v>
+        <v>141</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>271</v>
+        <v>167</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>84</v>
       </c>
@@ -5775,19 +5803,19 @@
         <v>84</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>274</v>
+        <v>171</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5799,7 +5827,7 @@
         <v>84</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>84</v>
@@ -5808,10 +5836,10 @@
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>275</v>
+        <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>276</v>
+        <v>165</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>84</v>
@@ -5828,10 +5856,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5839,31 +5867,35 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>161</v>
+        <v>276</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>162</v>
+        <v>277</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>84</v>
       </c>
@@ -5911,19 +5943,19 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>164</v>
+        <v>281</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>84</v>
@@ -5932,10 +5964,10 @@
         <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>84</v>
+        <v>282</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>165</v>
+        <v>283</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>84</v>
@@ -5952,21 +5984,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>84</v>
@@ -5978,17 +6010,15 @@
         <v>84</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -6025,31 +6055,31 @@
         <v>84</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>84</v>
@@ -6078,21 +6108,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>84</v>
@@ -6101,23 +6131,21 @@
         <v>84</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>280</v>
+        <v>141</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>281</v>
+        <v>167</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>84</v>
       </c>
@@ -6153,31 +6181,31 @@
         <v>84</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>284</v>
+        <v>171</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>84</v>
@@ -6186,10 +6214,10 @@
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>285</v>
+        <v>84</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>286</v>
+        <v>165</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>84</v>
@@ -6206,10 +6234,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6217,13 +6245,13 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>84</v>
@@ -6232,24 +6260,26 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>161</v>
+        <v>108</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>84</v>
+        <v>294</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>84</v>
@@ -6291,7 +6321,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6312,10 +6342,10 @@
         <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>84</v>
@@ -6332,10 +6362,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6349,7 +6379,7 @@
         <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>84</v>
@@ -6358,18 +6388,18 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>114</v>
+        <v>161</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>84</v>
       </c>
@@ -6378,7 +6408,7 @@
         <v>84</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>298</v>
+        <v>84</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>84</v>
@@ -6417,7 +6447,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6438,10 +6468,10 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>84</v>
@@ -6450,7 +6480,7 @@
         <v>84</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>302</v>
+        <v>84</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6458,10 +6488,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6469,13 +6499,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>84</v>
@@ -6484,24 +6514,24 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>84</v>
+        <v>311</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>84</v>
@@ -6543,7 +6573,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6564,10 +6594,10 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>84</v>
@@ -6584,10 +6614,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6610,19 +6640,17 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>311</v>
+        <v>161</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6671,7 +6699,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6692,10 +6720,10 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>84</v>
@@ -6712,10 +6740,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6738,19 +6766,19 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>161</v>
+        <v>325</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6799,7 +6827,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6820,10 +6848,10 @@
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>84</v>
@@ -6840,47 +6868,45 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J35" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="K35" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>257</v>
+        <v>335</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>258</v>
+        <v>336</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>259</v>
+        <v>337</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6905,13 +6931,13 @@
         <v>84</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>261</v>
+        <v>84</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>262</v>
+        <v>84</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>84</v>
@@ -6929,13 +6955,13 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>256</v>
+        <v>339</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>84</v>
@@ -6950,13 +6976,13 @@
         <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>84</v>
+        <v>340</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>264</v>
+        <v>341</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>265</v>
+        <v>84</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>84</v>
@@ -6970,42 +6996,46 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>266</v>
+        <v>342</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>84</v>
+        <v>343</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>162</v>
+        <v>344</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
       </c>
@@ -7029,13 +7059,13 @@
         <v>84</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>84</v>
+        <v>348</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>84</v>
+        <v>349</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -7053,10 +7083,10 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>164</v>
+        <v>342</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>94</v>
@@ -7065,25 +7095,25 @@
         <v>84</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>84</v>
+        <v>350</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>84</v>
+        <v>351</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>84</v>
+        <v>352</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>165</v>
+        <v>353</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>84</v>
+        <v>354</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>84</v>
+        <v>355</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -7094,21 +7124,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>330</v>
+        <v>356</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>267</v>
+        <v>356</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>84</v>
@@ -7120,17 +7150,15 @@
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -7167,31 +7195,31 @@
         <v>84</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>84</v>
@@ -7220,46 +7248,44 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>268</v>
+        <v>357</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>269</v>
+        <v>140</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>270</v>
+        <v>141</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>271</v>
+        <v>167</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>84</v>
       </c>
@@ -7295,19 +7321,19 @@
         <v>84</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>274</v>
+        <v>171</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7319,7 +7345,7 @@
         <v>84</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>84</v>
@@ -7328,10 +7354,10 @@
         <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>275</v>
+        <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>276</v>
+        <v>165</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>84</v>
@@ -7348,10 +7374,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>277</v>
+        <v>358</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7362,28 +7388,32 @@
         <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>161</v>
+        <v>276</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>162</v>
+        <v>277</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
       </c>
@@ -7407,13 +7437,11 @@
         <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>84</v>
+        <v>359</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -7431,19 +7459,19 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>164</v>
+        <v>281</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>84</v>
@@ -7452,10 +7480,10 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>84</v>
+        <v>282</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>165</v>
+        <v>283</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>84</v>
@@ -7464,7 +7492,7 @@
         <v>84</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>84</v>
+        <v>360</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>84</v>
@@ -7472,21 +7500,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>278</v>
+        <v>361</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>84</v>
@@ -7495,21 +7523,23 @@
         <v>84</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>141</v>
+        <v>335</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>167</v>
+        <v>336</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
       </c>
@@ -7545,31 +7575,31 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>171</v>
+        <v>339</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>84</v>
@@ -7578,10 +7608,10 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>84</v>
+        <v>340</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>165</v>
+        <v>341</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>84</v>
@@ -7598,10 +7628,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>334</v>
+        <v>362</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>279</v>
+        <v>362</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7624,26 +7654,26 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>108</v>
+        <v>363</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>280</v>
+        <v>364</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>281</v>
+        <v>365</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>282</v>
+        <v>366</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>283</v>
+        <v>367</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>335</v>
+        <v>84</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>84</v>
@@ -7685,7 +7715,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>284</v>
+        <v>362</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7700,25 +7730,25 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>84</v>
+        <v>368</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>285</v>
+        <v>369</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>286</v>
+        <v>370</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>84</v>
+        <v>371</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>84</v>
+        <v>372</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>84</v>
@@ -7726,10 +7756,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>287</v>
+        <v>373</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7740,7 +7770,7 @@
         <v>82</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>84</v>
@@ -7752,16 +7782,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>161</v>
+        <v>374</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>288</v>
+        <v>375</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>289</v>
+        <v>376</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>290</v>
+        <v>377</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7811,13 +7841,13 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>291</v>
+        <v>373</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>84</v>
@@ -7832,13 +7862,13 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>292</v>
+        <v>352</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>293</v>
+        <v>378</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>84</v>
+        <v>371</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>84</v>
@@ -7852,24 +7882,24 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>337</v>
+        <v>379</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>294</v>
+        <v>379</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>84</v>
+        <v>380</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>84</v>
@@ -7878,24 +7908,26 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>114</v>
+        <v>381</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>295</v>
+        <v>382</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="O43" t="s" s="2">
-        <v>297</v>
+        <v>385</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>298</v>
+        <v>84</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>84</v>
@@ -7937,7 +7969,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>299</v>
+        <v>379</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7952,19 +7984,19 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>84</v>
+        <v>386</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>301</v>
+        <v>388</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>84</v>
+        <v>389</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>84</v>
@@ -7978,24 +8010,24 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>338</v>
+        <v>390</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>303</v>
+        <v>390</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>84</v>
+        <v>391</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>84</v>
@@ -8004,17 +8036,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>161</v>
+        <v>392</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>304</v>
+        <v>393</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="O44" t="s" s="2">
-        <v>306</v>
+        <v>396</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -8051,19 +8085,17 @@
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>307</v>
+        <v>390</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8072,25 +8104,25 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>84</v>
+        <v>398</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>106</v>
+        <v>399</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>84</v>
+        <v>400</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>308</v>
+        <v>401</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>309</v>
+        <v>402</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>84</v>
+        <v>403</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>84</v>
@@ -8104,14 +8136,16 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>339</v>
+        <v>404</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="D45" t="s" s="2">
-        <v>84</v>
+        <v>391</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -8121,7 +8155,7 @@
         <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>84</v>
@@ -8130,19 +8164,19 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>311</v>
+        <v>406</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>312</v>
+        <v>393</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>313</v>
+        <v>394</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>314</v>
+        <v>395</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>315</v>
+        <v>396</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8191,7 +8225,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>316</v>
+        <v>390</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8200,42 +8234,42 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>84</v>
+        <v>398</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>106</v>
+        <v>399</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>84</v>
+        <v>400</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>317</v>
+        <v>401</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>318</v>
+        <v>402</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>84</v>
+        <v>403</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>84</v>
+        <v>407</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>84</v>
+        <v>408</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>319</v>
+        <v>409</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8249,7 +8283,7 @@
         <v>94</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>84</v>
@@ -8258,20 +8292,18 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>161</v>
+        <v>410</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>320</v>
+        <v>411</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>321</v>
+        <v>412</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>84</v>
       </c>
@@ -8319,7 +8351,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>324</v>
+        <v>409</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8340,41 +8372,41 @@
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>325</v>
+        <v>414</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>326</v>
+        <v>415</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>84</v>
+        <v>416</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>84</v>
+        <v>417</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>84</v>
+        <v>418</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>341</v>
+        <v>419</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>341</v>
+        <v>419</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>342</v>
+        <v>84</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>95</v>
@@ -8386,19 +8418,17 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>183</v>
+        <v>420</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>343</v>
+        <v>421</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>345</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>346</v>
+        <v>423</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8423,13 +8453,13 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>347</v>
+        <v>84</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>348</v>
+        <v>84</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -8447,13 +8477,13 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>341</v>
+        <v>419</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>84</v>
@@ -8462,25 +8492,25 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>349</v>
+        <v>424</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>350</v>
+        <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>351</v>
+        <v>425</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>352</v>
+        <v>426</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>353</v>
+        <v>427</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>354</v>
+        <v>84</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>84</v>
+        <v>428</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>84</v>
@@ -8488,10 +8518,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>355</v>
+        <v>429</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>355</v>
+        <v>429</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8499,7 +8529,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>94</v>
@@ -8514,19 +8544,19 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>356</v>
+        <v>430</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>357</v>
+        <v>431</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>358</v>
+        <v>432</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>359</v>
+        <v>433</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>360</v>
+        <v>434</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8551,31 +8581,29 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>84</v>
+        <v>435</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>84</v>
+        <v>436</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>355</v>
+        <v>429</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8584,31 +8612,31 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>84</v>
+        <v>437</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>361</v>
+        <v>84</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>84</v>
+        <v>438</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>362</v>
+        <v>439</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>363</v>
+        <v>440</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>364</v>
+        <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>84</v>
+        <v>441</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>365</v>
+        <v>84</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>84</v>
@@ -8616,12 +8644,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>366</v>
+        <v>442</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="D49" t="s" s="2">
         <v>84</v>
       </c>
@@ -8630,10 +8660,10 @@
         <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>84</v>
@@ -8642,18 +8672,20 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>367</v>
+        <v>444</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>368</v>
+        <v>431</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>369</v>
+        <v>432</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
       </c>
@@ -8677,13 +8709,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>84</v>
+        <v>435</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>84</v>
+        <v>436</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8701,16 +8733,16 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>366</v>
+        <v>429</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>84</v>
+        <v>437</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -8719,19 +8751,19 @@
         <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>84</v>
+        <v>438</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>351</v>
+        <v>439</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>371</v>
+        <v>440</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>364</v>
+        <v>84</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>84</v>
+        <v>441</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8742,14 +8774,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>372</v>
+        <v>445</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>372</v>
+        <v>446</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>373</v>
+        <v>84</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8765,23 +8797,19 @@
         <v>84</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>374</v>
+        <v>161</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>375</v>
+        <v>162</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>84</v>
       </c>
@@ -8829,7 +8857,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>372</v>
+        <v>164</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8841,22 +8869,22 @@
         <v>84</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>379</v>
+        <v>84</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>380</v>
+        <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>381</v>
+        <v>165</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>382</v>
+        <v>84</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>84</v>
@@ -8870,46 +8898,44 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>383</v>
+        <v>447</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>383</v>
+        <v>448</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>384</v>
+        <v>139</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>385</v>
+        <v>140</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>386</v>
+        <v>141</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>387</v>
+        <v>167</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>389</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>84</v>
       </c>
@@ -8945,9 +8971,11 @@
         <v>84</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AC51" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="AD51" t="s" s="2">
         <v>84</v>
       </c>
@@ -8955,34 +8983,34 @@
         <v>170</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>383</v>
+        <v>171</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>391</v>
+        <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>392</v>
+        <v>145</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>393</v>
+        <v>84</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>394</v>
+        <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>395</v>
+        <v>165</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>396</v>
+        <v>84</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>84</v>
@@ -8996,16 +9024,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>397</v>
+        <v>449</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>384</v>
+        <v>84</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -9024,19 +9050,19 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>399</v>
+        <v>451</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>386</v>
+        <v>452</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>387</v>
+        <v>453</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>388</v>
+        <v>454</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>389</v>
+        <v>455</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -9085,7 +9111,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>383</v>
+        <v>456</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9094,42 +9120,42 @@
         <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>391</v>
+        <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>392</v>
+        <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>393</v>
+        <v>84</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>394</v>
+        <v>457</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>395</v>
+        <v>458</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>396</v>
+        <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>400</v>
+        <v>459</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>401</v>
+        <v>460</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>402</v>
+        <v>461</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>402</v>
+        <v>462</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9143,31 +9169,33 @@
         <v>94</v>
       </c>
       <c r="H53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I53" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>403</v>
+        <v>114</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>404</v>
+        <v>463</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q53" s="2"/>
+      <c r="Q53" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="R53" t="s" s="2">
         <v>84</v>
       </c>
@@ -9187,13 +9215,13 @@
         <v>84</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>84</v>
+        <v>467</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>84</v>
+        <v>468</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>84</v>
@@ -9211,7 +9239,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>402</v>
+        <v>469</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9232,30 +9260,30 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>407</v>
+        <v>470</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>408</v>
+        <v>471</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>409</v>
+        <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>410</v>
+        <v>84</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>411</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>412</v>
+        <v>472</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>412</v>
+        <v>473</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9266,10 +9294,10 @@
         <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>84</v>
@@ -9278,17 +9306,17 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>413</v>
+        <v>161</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>414</v>
+        <v>474</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>415</v>
+        <v>475</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>416</v>
+        <v>476</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9337,13 +9365,13 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>412</v>
+        <v>477</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>84</v>
@@ -9352,25 +9380,25 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>417</v>
+        <v>84</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>418</v>
+        <v>478</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>419</v>
+        <v>479</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>420</v>
+        <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>421</v>
+        <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>84</v>
@@ -9378,10 +9406,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>422</v>
+        <v>480</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>422</v>
+        <v>481</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9395,7 +9423,7 @@
         <v>94</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>84</v>
@@ -9404,19 +9432,17 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>423</v>
+        <v>108</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>424</v>
+        <v>482</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>427</v>
+        <v>484</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9441,29 +9467,31 @@
         <v>84</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>428</v>
+        <v>84</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>429</v>
+        <v>84</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AC55" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>422</v>
+        <v>485</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9472,7 +9500,7 @@
         <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>430</v>
+        <v>486</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>106</v>
@@ -9481,19 +9509,19 @@
         <v>84</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>431</v>
+        <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>432</v>
+        <v>478</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>433</v>
+        <v>487</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>434</v>
+        <v>84</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9504,14 +9532,12 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>435</v>
+        <v>488</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>84</v>
       </c>
@@ -9532,19 +9558,19 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>437</v>
+        <v>114</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>424</v>
+        <v>490</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>425</v>
+        <v>491</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>426</v>
+        <v>492</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>427</v>
+        <v>493</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9569,13 +9595,13 @@
         <v>84</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>428</v>
+        <v>84</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>429</v>
+        <v>84</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -9593,7 +9619,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>422</v>
+        <v>494</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9602,7 +9628,7 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>430</v>
+        <v>84</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9611,22 +9637,22 @@
         <v>84</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>431</v>
+        <v>84</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>432</v>
+        <v>478</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>433</v>
+        <v>495</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>434</v>
+        <v>84</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>84</v>
+        <v>496</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>84</v>
@@ -9634,10 +9660,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>438</v>
+        <v>497</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>439</v>
+        <v>498</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9663,10 +9689,10 @@
         <v>161</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>162</v>
+        <v>499</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>163</v>
+        <v>500</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9741,7 +9767,7 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>165</v>
+        <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
@@ -9758,14 +9784,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>440</v>
+        <v>501</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>441</v>
+        <v>502</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9787,14 +9813,12 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>141</v>
+        <v>503</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9833,9 +9857,7 @@
       <c r="AB58" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AC58" t="s" s="2">
-        <v>169</v>
-      </c>
+      <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>84</v>
       </c>
@@ -9867,7 +9889,7 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>165</v>
+        <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>84</v>
@@ -9884,12 +9906,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>442</v>
+        <v>505</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>502</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>506</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>84</v>
       </c>
@@ -9901,29 +9925,27 @@
         <v>94</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>444</v>
+        <v>507</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>445</v>
+        <v>508</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>446</v>
+        <v>509</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>84</v>
       </c>
@@ -9971,19 +9993,19 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>449</v>
+        <v>171</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>84</v>
+        <v>511</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>84</v>
@@ -9992,10 +10014,10 @@
         <v>84</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>450</v>
+        <v>137</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>451</v>
+        <v>137</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>84</v>
@@ -10004,18 +10026,18 @@
         <v>84</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>452</v>
+        <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>453</v>
+        <v>84</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>454</v>
+        <v>512</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10032,30 +10054,26 @@
         <v>84</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>114</v>
+        <v>161</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>456</v>
+        <v>162</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>457</v>
+        <v>163</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>458</v>
-      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q60" t="s" s="2">
-        <v>459</v>
-      </c>
+      <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
         <v>84</v>
       </c>
@@ -10075,13 +10093,13 @@
         <v>84</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>177</v>
+        <v>84</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>460</v>
+        <v>84</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>461</v>
+        <v>84</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>84</v>
@@ -10099,7 +10117,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>462</v>
+        <v>164</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10111,7 +10129,7 @@
         <v>84</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>84</v>
@@ -10120,10 +10138,10 @@
         <v>84</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>463</v>
+        <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>464</v>
+        <v>165</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>84</v>
@@ -10140,10 +10158,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>465</v>
+        <v>514</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>466</v>
+        <v>515</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10154,7 +10172,7 @@
         <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>84</v>
@@ -10163,21 +10181,19 @@
         <v>84</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>467</v>
+        <v>503</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>468</v>
+        <v>504</v>
       </c>
       <c r="N61" s="2"/>
-      <c r="O61" t="s" s="2">
-        <v>469</v>
-      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>84</v>
       </c>
@@ -10213,31 +10229,31 @@
         <v>84</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>470</v>
+        <v>171</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>84</v>
@@ -10246,10 +10262,10 @@
         <v>84</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>471</v>
+        <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>472</v>
+        <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>84</v>
@@ -10266,10 +10282,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>473</v>
+        <v>516</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>474</v>
+        <v>517</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10277,7 +10293,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>94</v>
@@ -10289,27 +10305,27 @@
         <v>84</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>475</v>
+        <v>518</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>519</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>84</v>
+        <v>521</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>84</v>
@@ -10351,19 +10367,19 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>478</v>
+        <v>522</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>479</v>
+        <v>84</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>84</v>
@@ -10372,10 +10388,10 @@
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>471</v>
+        <v>84</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>480</v>
+        <v>137</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>84</v>
@@ -10392,10 +10408,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>481</v>
+        <v>523</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>482</v>
+        <v>524</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10403,35 +10419,31 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>114</v>
+        <v>525</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>483</v>
+        <v>526</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>486</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>84</v>
       </c>
@@ -10440,7 +10452,7 @@
         <v>84</v>
       </c>
       <c r="S63" t="s" s="2">
-        <v>84</v>
+        <v>528</v>
       </c>
       <c r="T63" t="s" s="2">
         <v>84</v>
@@ -10479,7 +10491,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>487</v>
+        <v>529</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10500,10 +10512,10 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>471</v>
+        <v>84</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>488</v>
+        <v>137</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>
@@ -10512,7 +10524,7 @@
         <v>84</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>489</v>
+        <v>84</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>84</v>
@@ -10520,10 +10532,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>490</v>
+        <v>530</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>491</v>
+        <v>531</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10549,10 +10561,10 @@
         <v>161</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>492</v>
+        <v>532</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>493</v>
+        <v>532</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10603,7 +10615,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>164</v>
+        <v>533</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10644,10 +10656,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>494</v>
+        <v>534</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>495</v>
+        <v>534</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10658,10 +10670,10 @@
         <v>82</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>84</v>
@@ -10670,16 +10682,20 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>496</v>
+        <v>535</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
       </c>
@@ -10703,41 +10719,43 @@
         <v>84</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>84</v>
+        <v>539</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>84</v>
+        <v>540</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AC65" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>171</v>
+        <v>534</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>84</v>
+        <v>541</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>84</v>
@@ -10746,10 +10764,10 @@
         <v>84</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>84</v>
+        <v>542</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>84</v>
@@ -10766,23 +10784,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>498</v>
+        <v>543</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>499</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>84</v>
+        <v>544</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>84</v>
@@ -10794,18 +10810,20 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>500</v>
+        <v>183</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>501</v>
+        <v>545</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>502</v>
+        <v>546</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>547</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>548</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
       </c>
@@ -10829,13 +10847,13 @@
         <v>84</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>84</v>
+        <v>549</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>84</v>
+        <v>550</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>84</v>
@@ -10853,7 +10871,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>171</v>
+        <v>543</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10862,28 +10880,28 @@
         <v>83</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>504</v>
+        <v>84</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>84</v>
+        <v>551</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>137</v>
+        <v>552</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>137</v>
+        <v>553</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>84</v>
+        <v>554</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -10894,10 +10912,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>505</v>
+        <v>555</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>506</v>
+        <v>555</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10908,7 +10926,7 @@
         <v>82</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>84</v>
@@ -10920,16 +10938,20 @@
         <v>84</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>161</v>
+        <v>556</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>162</v>
+        <v>557</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+        <v>558</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>560</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
       </c>
@@ -10977,19 +10999,19 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>164</v>
+        <v>555</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>84</v>
@@ -10998,10 +11020,10 @@
         <v>84</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>84</v>
+        <v>561</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>165</v>
+        <v>562</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>84</v>
@@ -11018,10 +11040,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>507</v>
+        <v>563</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>508</v>
+        <v>563</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11032,7 +11054,7 @@
         <v>82</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>84</v>
@@ -11044,15 +11066,17 @@
         <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>496</v>
+        <v>564</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>565</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>566</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -11077,61 +11101,61 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>84</v>
+        <v>567</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>84</v>
+        <v>568</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>84</v>
+        <v>569</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>171</v>
+        <v>563</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>84</v>
+        <v>570</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>84</v>
+        <v>571</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>84</v>
+        <v>572</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>84</v>
+        <v>573</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -11142,10 +11166,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>509</v>
+        <v>574</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>510</v>
+        <v>574</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11153,13 +11177,13 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>84</v>
@@ -11168,24 +11192,26 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>108</v>
+        <v>183</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>511</v>
+        <v>575</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>512</v>
+        <v>576</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>514</v>
+        <v>84</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>84</v>
@@ -11203,13 +11229,11 @@
         <v>84</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>84</v>
+        <v>579</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -11227,10 +11251,10 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>515</v>
+        <v>574</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>94</v>
@@ -11239,7 +11263,7 @@
         <v>84</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>84</v>
@@ -11248,10 +11272,10 @@
         <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>84</v>
+        <v>580</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>137</v>
+        <v>581</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>84</v>
@@ -11260,7 +11284,7 @@
         <v>84</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>84</v>
+        <v>582</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>84</v>
@@ -11268,10 +11292,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>516</v>
+        <v>583</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>517</v>
+        <v>583</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11279,7 +11303,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>94</v>
@@ -11294,15 +11318,17 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>518</v>
+        <v>584</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>519</v>
+        <v>585</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>586</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>587</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11312,7 +11338,7 @@
         <v>84</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>521</v>
+        <v>84</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>84</v>
@@ -11351,7 +11377,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>522</v>
+        <v>583</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11369,19 +11395,19 @@
         <v>84</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>84</v>
+        <v>588</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>84</v>
+        <v>589</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>137</v>
+        <v>590</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>84</v>
+        <v>591</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11392,10 +11418,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>523</v>
+        <v>592</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>524</v>
+        <v>592</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11409,7 +11435,7 @@
         <v>94</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>84</v>
@@ -11418,15 +11444,17 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>161</v>
+        <v>593</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>525</v>
+        <v>594</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>595</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>596</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11475,7 +11503,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>526</v>
+        <v>592</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11487,28 +11515,28 @@
         <v>84</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>84</v>
+        <v>597</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>84</v>
+        <v>598</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>84</v>
+        <v>599</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>84</v>
+        <v>600</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>84</v>
+        <v>601</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>84</v>
@@ -11516,10 +11544,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>527</v>
+        <v>602</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>527</v>
+        <v>602</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11530,10 +11558,10 @@
         <v>82</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>84</v>
@@ -11542,19 +11570,19 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>183</v>
+        <v>603</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>528</v>
+        <v>604</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>529</v>
+        <v>605</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>530</v>
+        <v>606</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>531</v>
+        <v>607</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11579,13 +11607,13 @@
         <v>84</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>532</v>
+        <v>84</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>533</v>
+        <v>84</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>84</v>
@@ -11603,19 +11631,19 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>527</v>
+        <v>602</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>534</v>
+        <v>84</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>106</v>
+        <v>608</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>84</v>
@@ -11624,10 +11652,10 @@
         <v>84</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>137</v>
+        <v>609</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>535</v>
+        <v>610</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>84</v>
@@ -11644,21 +11672,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>536</v>
+        <v>611</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>536</v>
+        <v>611</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>537</v>
+        <v>84</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>84</v>
@@ -11670,20 +11698,16 @@
         <v>84</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>538</v>
+        <v>162</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>541</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>84</v>
       </c>
@@ -11707,13 +11731,13 @@
         <v>84</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>542</v>
+        <v>84</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>543</v>
+        <v>84</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>84</v>
@@ -11731,37 +11755,37 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>536</v>
+        <v>164</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>544</v>
+        <v>84</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>545</v>
+        <v>84</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>546</v>
+        <v>165</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>547</v>
+        <v>84</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
@@ -11772,14 +11796,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>548</v>
+        <v>612</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>548</v>
+        <v>612</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11798,20 +11822,18 @@
         <v>84</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>549</v>
+        <v>140</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>550</v>
+        <v>141</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>551</v>
+        <v>167</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>553</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>84</v>
       </c>
@@ -11859,7 +11881,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>548</v>
+        <v>171</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11871,7 +11893,7 @@
         <v>84</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>84</v>
@@ -11880,10 +11902,10 @@
         <v>84</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>554</v>
+        <v>84</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>555</v>
+        <v>165</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>84</v>
@@ -11900,44 +11922,46 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>556</v>
+        <v>613</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>556</v>
+        <v>613</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>84</v>
+        <v>614</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>557</v>
+        <v>615</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>558</v>
+        <v>616</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>84</v>
       </c>
@@ -11961,13 +11985,13 @@
         <v>84</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>560</v>
+        <v>84</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>561</v>
+        <v>84</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>562</v>
+        <v>84</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>84</v>
@@ -11985,37 +12009,37 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>556</v>
+        <v>617</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>563</v>
+        <v>84</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>564</v>
+        <v>84</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>565</v>
+        <v>137</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>566</v>
+        <v>84</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
@@ -12026,10 +12050,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>567</v>
+        <v>618</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>567</v>
+        <v>618</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12043,7 +12067,7 @@
         <v>94</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>84</v>
@@ -12052,20 +12076,16 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>183</v>
+        <v>619</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>568</v>
+        <v>620</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>84</v>
       </c>
@@ -12089,11 +12109,13 @@
         <v>84</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y76" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z76" t="s" s="2">
-        <v>572</v>
+        <v>84</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -12111,7 +12133,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>567</v>
+        <v>618</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12120,7 +12142,7 @@
         <v>94</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>84</v>
+        <v>622</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>106</v>
@@ -12132,10 +12154,10 @@
         <v>84</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>573</v>
+        <v>623</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>574</v>
+        <v>624</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>84</v>
@@ -12144,7 +12166,7 @@
         <v>84</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>575</v>
+        <v>84</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>84</v>
@@ -12152,10 +12174,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>576</v>
+        <v>625</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>576</v>
+        <v>625</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12178,17 +12200,15 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>577</v>
+        <v>619</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>578</v>
+        <v>626</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>580</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12237,7 +12257,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>576</v>
+        <v>625</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12246,7 +12266,7 @@
         <v>94</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>84</v>
+        <v>622</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>106</v>
@@ -12255,19 +12275,19 @@
         <v>84</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>581</v>
+        <v>84</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>582</v>
+        <v>623</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>583</v>
+        <v>628</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>584</v>
+        <v>84</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12278,10 +12298,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>585</v>
+        <v>629</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>585</v>
+        <v>629</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12295,7 +12315,7 @@
         <v>94</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>84</v>
@@ -12304,18 +12324,20 @@
         <v>84</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>586</v>
+        <v>183</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>587</v>
+        <v>630</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>588</v>
+        <v>631</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>632</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>633</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
       </c>
@@ -12339,13 +12361,13 @@
         <v>84</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>84</v>
+        <v>634</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>84</v>
+        <v>635</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
@@ -12363,7 +12385,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>585</v>
+        <v>629</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12381,22 +12403,22 @@
         <v>84</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>590</v>
+        <v>636</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>591</v>
+        <v>637</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>592</v>
+        <v>553</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>593</v>
+        <v>84</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>594</v>
+        <v>84</v>
       </c>
       <c r="AR78" t="s" s="2">
         <v>84</v>
@@ -12404,10 +12426,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>595</v>
+        <v>638</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>595</v>
+        <v>638</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12430,19 +12452,19 @@
         <v>84</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>596</v>
+        <v>183</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>597</v>
+        <v>639</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>598</v>
+        <v>640</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>599</v>
+        <v>641</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>600</v>
+        <v>642</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -12467,13 +12489,13 @@
         <v>84</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>84</v>
+        <v>567</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>84</v>
+        <v>643</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>84</v>
+        <v>644</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>84</v>
@@ -12491,7 +12513,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>595</v>
+        <v>638</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12503,19 +12525,19 @@
         <v>84</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>601</v>
+        <v>106</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>84</v>
+        <v>636</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>602</v>
+        <v>637</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>603</v>
+        <v>553</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>84</v>
@@ -12532,10 +12554,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>604</v>
+        <v>645</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>604</v>
+        <v>645</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12558,16 +12580,18 @@
         <v>84</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>161</v>
+        <v>646</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>162</v>
+        <v>647</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>163</v>
+        <v>648</v>
       </c>
       <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+      <c r="O80" t="s" s="2">
+        <v>649</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
       </c>
@@ -12615,7 +12639,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>164</v>
+        <v>645</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12627,7 +12651,7 @@
         <v>84</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>84</v>
@@ -12639,7 +12663,7 @@
         <v>84</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>165</v>
+        <v>650</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>84</v>
@@ -12656,21 +12680,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>605</v>
+        <v>651</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>605</v>
+        <v>651</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>84</v>
@@ -12682,17 +12706,15 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>141</v>
+        <v>652</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>653</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>84</v>
@@ -12741,19 +12763,19 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>84</v>
@@ -12762,10 +12784,10 @@
         <v>84</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>84</v>
+        <v>623</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>165</v>
+        <v>654</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>84</v>
@@ -12782,14 +12804,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>606</v>
+        <v>655</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>606</v>
+        <v>655</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>607</v>
+        <v>84</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12802,26 +12824,24 @@
         <v>84</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J82" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>140</v>
+        <v>656</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>608</v>
+        <v>657</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>609</v>
+        <v>658</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>84</v>
       </c>
@@ -12869,7 +12889,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>610</v>
+        <v>655</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12881,7 +12901,7 @@
         <v>84</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>84</v>
@@ -12890,10 +12910,10 @@
         <v>84</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>84</v>
+        <v>660</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>137</v>
+        <v>661</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>84</v>
@@ -12910,10 +12930,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>611</v>
+        <v>662</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>611</v>
+        <v>662</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12924,7 +12944,7 @@
         <v>82</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>84</v>
@@ -12933,18 +12953,20 @@
         <v>84</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>612</v>
+        <v>663</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>613</v>
+        <v>664</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>665</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>666</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>84</v>
@@ -12993,16 +13015,16 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>611</v>
+        <v>662</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>615</v>
+        <v>84</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>106</v>
@@ -13014,10 +13036,10 @@
         <v>84</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>616</v>
+        <v>660</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>617</v>
+        <v>667</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>84</v>
@@ -13034,10 +13056,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>618</v>
+        <v>668</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>618</v>
+        <v>668</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13048,28 +13070,32 @@
         <v>82</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>619</v>
+        <v>669</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>670</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>672</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>84</v>
       </c>
@@ -13117,19 +13143,19 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>618</v>
+        <v>668</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>615</v>
+        <v>84</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>106</v>
+        <v>673</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>84</v>
@@ -13138,10 +13164,10 @@
         <v>84</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>616</v>
+        <v>674</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>621</v>
+        <v>675</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>84</v>
@@ -13158,10 +13184,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>622</v>
+        <v>676</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>622</v>
+        <v>676</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13184,20 +13210,16 @@
         <v>84</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>623</v>
+        <v>162</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>626</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>84</v>
       </c>
@@ -13221,13 +13243,13 @@
         <v>84</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>627</v>
+        <v>84</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>628</v>
+        <v>84</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>84</v>
@@ -13245,7 +13267,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>622</v>
+        <v>164</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13257,19 +13279,19 @@
         <v>84</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>629</v>
+        <v>84</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>630</v>
+        <v>84</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>546</v>
+        <v>165</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>84</v>
@@ -13286,14 +13308,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>631</v>
+        <v>677</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>631</v>
+        <v>677</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -13312,20 +13334,18 @@
         <v>84</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>632</v>
+        <v>141</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>633</v>
+        <v>167</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>635</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>84</v>
       </c>
@@ -13349,13 +13369,13 @@
         <v>84</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>560</v>
+        <v>84</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>636</v>
+        <v>84</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>637</v>
+        <v>84</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>84</v>
@@ -13373,7 +13393,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>631</v>
+        <v>171</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13385,19 +13405,19 @@
         <v>84</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>629</v>
+        <v>84</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>630</v>
+        <v>84</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>546</v>
+        <v>165</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>84</v>
@@ -13414,43 +13434,45 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>638</v>
+        <v>678</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>638</v>
+        <v>678</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>84</v>
+        <v>614</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>639</v>
+        <v>140</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>640</v>
+        <v>615</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>616</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O87" t="s" s="2">
-        <v>642</v>
+        <v>149</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>84</v>
@@ -13499,19 +13521,19 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>638</v>
+        <v>617</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>84</v>
@@ -13523,7 +13545,7 @@
         <v>84</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>643</v>
+        <v>137</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>84</v>
@@ -13540,10 +13562,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>644</v>
+        <v>679</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>644</v>
+        <v>679</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13551,31 +13573,35 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>645</v>
+        <v>680</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
+        <v>681</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>683</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>84</v>
       </c>
@@ -13599,13 +13625,13 @@
         <v>84</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>84</v>
+        <v>348</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>84</v>
+        <v>349</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>84</v>
@@ -13623,10 +13649,10 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>644</v>
+        <v>679</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>94</v>
@@ -13641,16 +13667,16 @@
         <v>84</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>84</v>
+        <v>684</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>616</v>
+        <v>352</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>647</v>
+        <v>353</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>84</v>
+        <v>354</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>84</v>
@@ -13664,10 +13690,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>648</v>
+        <v>685</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>648</v>
+        <v>685</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13678,10 +13704,10 @@
         <v>82</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>84</v>
@@ -13690,18 +13716,20 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>649</v>
+        <v>430</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>650</v>
+        <v>686</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>651</v>
+        <v>687</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="O89" s="2"/>
+        <v>688</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
       </c>
@@ -13725,13 +13753,13 @@
         <v>84</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>84</v>
+        <v>435</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>84</v>
+        <v>436</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>84</v>
@@ -13749,16 +13777,16 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>648</v>
+        <v>685</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>84</v>
+        <v>689</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>106</v>
@@ -13767,19 +13795,19 @@
         <v>84</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>84</v>
+        <v>690</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>653</v>
+        <v>439</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>654</v>
+        <v>440</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>84</v>
+        <v>441</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -13790,10 +13818,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>655</v>
+        <v>691</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>655</v>
+        <v>691</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13804,30 +13832,32 @@
         <v>82</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>656</v>
+        <v>183</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>657</v>
+        <v>692</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>658</v>
+        <v>693</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>694</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>84</v>
       </c>
@@ -13851,13 +13881,13 @@
         <v>84</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>84</v>
+        <v>539</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>84</v>
+        <v>540</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>84</v>
@@ -13875,16 +13905,16 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>655</v>
+        <v>691</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>84</v>
+        <v>695</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>106</v>
@@ -13896,10 +13926,10 @@
         <v>84</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>653</v>
+        <v>137</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>660</v>
+        <v>542</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>84</v>
@@ -13916,14 +13946,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>661</v>
+        <v>696</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>661</v>
+        <v>696</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>84</v>
+        <v>544</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13933,28 +13963,28 @@
         <v>83</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>596</v>
+        <v>183</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>662</v>
+        <v>545</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>663</v>
+        <v>546</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>664</v>
+        <v>547</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>665</v>
+        <v>548</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>84</v>
@@ -13979,13 +14009,13 @@
         <v>84</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>84</v>
+        <v>549</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>84</v>
+        <v>550</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>84</v>
@@ -14003,7 +14033,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>661</v>
+        <v>696</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14015,25 +14045,25 @@
         <v>84</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>666</v>
+        <v>106</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>84</v>
+        <v>551</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>667</v>
+        <v>552</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>668</v>
+        <v>553</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>84</v>
+        <v>554</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
@@ -14044,10 +14074,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>669</v>
+        <v>697</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>669</v>
+        <v>697</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14058,7 +14088,7 @@
         <v>82</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>84</v>
@@ -14070,16 +14100,20 @@
         <v>84</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>162</v>
+        <v>698</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+        <v>699</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>607</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>84</v>
       </c>
@@ -14127,19 +14161,19 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>164</v>
+        <v>697</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>84</v>
@@ -14148,10 +14182,10 @@
         <v>84</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>84</v>
+        <v>609</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>165</v>
+        <v>610</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>84</v>
@@ -14163,905 +14197,11 @@
         <v>84</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="93" hidden="true">
-      <c r="A93" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O93" s="2"/>
-      <c r="P93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q93" s="2"/>
-      <c r="R93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR93" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="94" hidden="true">
-      <c r="A94" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="E94" s="2"/>
-      <c r="F94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="P94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q94" s="2"/>
-      <c r="R94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR94" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="95" hidden="true">
-      <c r="A95" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="P95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q95" s="2"/>
-      <c r="R95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR95" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="P96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AQ96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR96" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="P97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR97" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="98" hidden="true">
-      <c r="A98" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="AQ98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR98" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="P99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR99" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR99">
+  <autoFilter ref="A1:AR92">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15071,7 +14211,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI98">
+  <conditionalFormatting sqref="A2:AI91">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1287,8 +1287,7 @@
     <t>657: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS TAKEN (#120.5-.01)</t>
   </si>
   <si>
-    <t>Vital.VitalSign.VitalSignTakenDateTime
-Vital.VitalSignQualifier.VitalSignTakenDateTime</t>
+    <t>Vital.VitalSign.VitalSignTakenDateTime,Vital.VitalSignQualifier.VitalSignTakenDateTime</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -1450,10 +1449,7 @@
     <t>664: source value from GMRV VITAL MEASUREMENT - RATE (#120.5-1.2) case VUID not = 4500634</t>
   </si>
   <si>
-    <t>Vital.VitalSign.Diastolic
-Vital.VitalSign.Systolic
-Vital.VitalSign.VitalResult
-Vital.VitalSign.VitalResultNumeric</t>
+    <t>Vital.VitalSign.Diastolic,Vital.VitalSign.Systolic,Vital.VitalSign.VitalResult,Vital.VitalSign.VitalResultNumeric</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity.comparator</t>
@@ -2563,7 +2559,7 @@
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
     <col min="43" max="43" width="117.765625" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="44.85546875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="98.75" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -253,12 +259,6 @@
   </si>
   <si>
     <t>Mapping: SNOMED CT Attribute Binding</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -662,13 +662,13 @@
     <t>Identifier.value</t>
   </si>
   <si>
+    <t>660: source value from GMRV VITAL MEASUREMENT - IEN (#120.5-.001)</t>
+  </si>
+  <si>
     <t>CX.1 / EI.1</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>660: source value from GMRV VITAL MEASUREMENT - IEN (#120.5-.001)</t>
   </si>
   <si>
     <t>Observation.identifier.period</t>
@@ -794,6 +794,9 @@
     <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
   </si>
   <si>
+    <t>656: transform using #entered-in-error on GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (#120.5-4) case not null</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -807,9 +810,6 @@
   </si>
   <si>
     <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>656: transform using #entered-in-error on GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (#120.5-4) case not null</t>
   </si>
   <si>
     <t>Observation.category</t>
@@ -845,13 +845,13 @@
 value:coding.system}</t>
   </si>
   <si>
+    <t>658: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#vital-signs</t>
+  </si>
+  <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
   </si>
   <si>
     <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>658: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#vital-signs</t>
   </si>
   <si>
     <t>Observation.category:VSCat</t>
@@ -1158,6 +1158,9 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
+    <t>659: reference from GMRV VITAL MEASUREMENT - PATIENT (#120.5-.02)</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1168,9 +1171,6 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>659: reference from GMRV VITAL MEASUREMENT - PATIENT (#120.5-.02)</t>
   </si>
   <si>
     <t>Observation.focus</t>
@@ -1306,6 +1306,12 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
+    <t>652: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS ENTERED (#120.5-.04)</t>
+  </si>
+  <si>
+    <t>Vital.VitalSign.VitalSignEnteredDateTime</t>
+  </si>
+  <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
   </si>
   <si>
@@ -1313,12 +1319,6 @@
   </si>
   <si>
     <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>652: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS ENTERED (#120.5-.04)</t>
-  </si>
-  <si>
-    <t>Vital.VitalSign.VitalSignEnteredDateTime</t>
   </si>
   <si>
     <t>Observation.performer</t>
@@ -1337,6 +1337,9 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
+    <t>1653: reference from GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (#120.5-.05)</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1347,9 +1350,6 @@
   </si>
   <si>
     <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>1653: reference from GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (#120.5-.05)</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -1440,16 +1440,16 @@
     <t>Quantity.value</t>
   </si>
   <si>
+    <t>664: source value from GMRV VITAL MEASUREMENT - RATE (#120.5-1.2) case VUID not = 4500634</t>
+  </si>
+  <si>
+    <t>Vital.VitalSign.Diastolic,Vital.VitalSign.Systolic,Vital.VitalSign.VitalResult,Vital.VitalSign.VitalResultNumeric</t>
+  </si>
+  <si>
     <t>SN.2  / CQ - N/A</t>
   </si>
   <si>
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
-  </si>
-  <si>
-    <t>664: source value from GMRV VITAL MEASUREMENT - RATE (#120.5-1.2) case VUID not = 4500634</t>
-  </si>
-  <si>
-    <t>Vital.VitalSign.Diastolic,Vital.VitalSign.Systolic,Vital.VitalSign.VitalResult,Vital.VitalSign.VitalResultNumeric</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity.comparator</t>
@@ -1555,10 +1555,10 @@
     <t>Quantity.code</t>
   </si>
   <si>
+    <t>665: transform using VF_VitalsUnits on GMRV VITAL MEASUREMENT - VITAL TYPE (#120.5-.03)</t>
+  </si>
+  <si>
     <t>PQ.code, MO.currency, PQ.translation.code</t>
-  </si>
-  <si>
-    <t>665: transform using VF_VitalsUnits on GMRV VITAL MEASUREMENT - VITAL TYPE (#120.5-.03)</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity.code.id</t>
@@ -1818,13 +1818,13 @@
     <t>http://va.gov/fhir/ValueSet/VSVFVitalsMethod</t>
   </si>
   <si>
+    <t>867: terminologyMaps using VF_VitalsMethod on GMRV VITAL MEASUREMENT - QUALIFIER (#120.5-5)</t>
+  </si>
+  <si>
     <t>OBX-17</t>
   </si>
   <si>
     <t>methodCode</t>
-  </si>
-  <si>
-    <t>867: terminologyMaps using VF_VitalsMethod on GMRV VITAL MEASUREMENT - QUALIFIER (#120.5-5)</t>
   </si>
   <si>
     <t>Observation.specimen</t>
@@ -1871,6 +1871,9 @@
     <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
   </si>
   <si>
+    <t>1655: reference from GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (#120.5-5 &gt; 120.52-99.99)</t>
+  </si>
+  <si>
     <t>&lt; 49062001 |Device|</t>
   </si>
   <si>
@@ -1881,9 +1884,6 @@
   </si>
   <si>
     <t>424226004 |Using device|</t>
-  </si>
-  <si>
-    <t>1655: reference from GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (#120.5-5 &gt; 120.52-99.99)</t>
   </si>
   <si>
     <t>Observation.referenceRange</t>
@@ -2552,14 +2552,14 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="117.765625" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="98.75" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="117.765625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="98.75" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2798,22 +2798,22 @@
         <v>88</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AN2" t="s" s="2">
+      <c r="AP2" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP2" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ2" t="s" s="2">
         <v>84</v>
@@ -3435,13 +3435,13 @@
         <v>84</v>
       </c>
       <c r="AN7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP7" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ7" t="s" s="2">
         <v>84</v>
@@ -3561,13 +3561,13 @@
         <v>84</v>
       </c>
       <c r="AN8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP8" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ8" t="s" s="2">
         <v>84</v>
@@ -3687,13 +3687,13 @@
         <v>84</v>
       </c>
       <c r="AN9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP9" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ9" t="s" s="2">
         <v>84</v>
@@ -3815,13 +3815,13 @@
         <v>84</v>
       </c>
       <c r="AN10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP10" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP10" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ10" t="s" s="2">
         <v>84</v>
@@ -3932,25 +3932,25 @@
         <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AQ11" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ11" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR11" t="s" s="2">
         <v>84</v>
@@ -4065,13 +4065,13 @@
         <v>84</v>
       </c>
       <c r="AN12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP12" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>84</v>
@@ -4191,13 +4191,13 @@
         <v>84</v>
       </c>
       <c r="AN13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP13" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>84</v>
@@ -4316,16 +4316,16 @@
         <v>84</v>
       </c>
       <c r="AM14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO14" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ14" t="s" s="2">
         <v>84</v>
@@ -4444,16 +4444,16 @@
         <v>84</v>
       </c>
       <c r="AM15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AP15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>84</v>
@@ -4572,16 +4572,16 @@
         <v>84</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>84</v>
@@ -4692,25 +4692,25 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>84</v>
+        <v>208</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="AN17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AO17" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP17" t="s" s="2">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>210</v>
+        <v>84</v>
       </c>
       <c r="AR17" t="s" s="2">
         <v>84</v>
@@ -4822,16 +4822,16 @@
         <v>84</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AP18" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>84</v>
@@ -4948,16 +4948,16 @@
         <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
@@ -5068,22 +5068,22 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
@@ -5194,22 +5194,22 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>84</v>
@@ -5323,19 +5323,19 @@
         <v>250</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AO22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>255</v>
@@ -5446,7 +5446,7 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>84</v>
+        <v>265</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>84</v>
@@ -5455,13 +5455,13 @@
         <v>84</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>265</v>
+        <v>84</v>
       </c>
       <c r="AO23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP23" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>267</v>
@@ -5585,16 +5585,16 @@
         <v>84</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>265</v>
+        <v>84</v>
       </c>
       <c r="AO24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AP24" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AQ24" t="s" s="2">
-        <v>84</v>
+        <v>267</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5709,13 +5709,13 @@
         <v>84</v>
       </c>
       <c r="AN25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP25" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>84</v>
@@ -5835,13 +5835,13 @@
         <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>84</v>
@@ -5960,16 +5960,16 @@
         <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
@@ -6087,13 +6087,13 @@
         <v>84</v>
       </c>
       <c r="AN28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -6213,13 +6213,13 @@
         <v>84</v>
       </c>
       <c r="AN29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP29" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -6338,16 +6338,16 @@
         <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>84</v>
@@ -6464,16 +6464,16 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -6590,16 +6590,16 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6716,16 +6716,16 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6844,16 +6844,16 @@
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6972,16 +6972,16 @@
         <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -7094,28 +7094,28 @@
         <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AO36" t="s" s="2">
+      <c r="AQ36" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AP36" t="s" s="2">
+      <c r="AR36" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AQ36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR36" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="37" hidden="true">
@@ -7227,13 +7227,13 @@
         <v>84</v>
       </c>
       <c r="AN37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -7353,13 +7353,13 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP38" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -7470,25 +7470,25 @@
         <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>84</v>
+        <v>360</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AO39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AQ39" t="s" s="2">
-        <v>360</v>
+        <v>84</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>84</v>
@@ -7604,16 +7604,16 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7735,13 +7735,13 @@
         <v>369</v>
       </c>
       <c r="AN41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AO41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>372</v>
@@ -7858,19 +7858,19 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AO42" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AQ42" t="s" s="2">
-        <v>84</v>
+        <v>372</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -7980,25 +7980,25 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AL43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AO43" t="s" s="2">
+      <c r="AQ43" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>84</v>
@@ -8106,25 +8106,25 @@
         <v>399</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AL44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AO44" t="s" s="2">
+      <c r="AQ44" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>84</v>
@@ -8236,28 +8236,28 @@
         <v>399</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AL45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM45" t="s" s="2">
+      <c r="AN45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AP45" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AO45" t="s" s="2">
+      <c r="AQ45" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AP45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ45" t="s" s="2">
-        <v>407</v>
-      </c>
       <c r="AR45" t="s" s="2">
-        <v>408</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" hidden="true">
@@ -8362,28 +8362,28 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>84</v>
+        <v>414</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>84</v>
+        <v>415</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>414</v>
+        <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>415</v>
+        <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>416</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>84</v>
+        <v>417</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>418</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -8497,13 +8497,13 @@
         <v>425</v>
       </c>
       <c r="AN47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AO47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>428</v>
@@ -8617,25 +8617,25 @@
         <v>84</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AO48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP48" t="s" s="2">
+      <c r="AQ48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR48" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR48" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="49" hidden="true">
@@ -8747,25 +8747,25 @@
         <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AO49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP49" t="s" s="2">
+      <c r="AQ49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR49" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR49" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -8877,13 +8877,13 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -9003,13 +9003,13 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -9122,28 +9122,28 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>84</v>
+        <v>457</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>84</v>
+        <v>458</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>457</v>
+        <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>458</v>
+        <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>84</v>
+        <v>459</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>84</v>
+        <v>460</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>459</v>
+        <v>84</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>460</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" hidden="true">
@@ -9256,16 +9256,16 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AP53" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -9382,16 +9382,16 @@
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AP54" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -9508,16 +9508,16 @@
         <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AP55" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9630,25 +9630,25 @@
         <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>84</v>
+        <v>495</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="AN56" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP56" t="s" s="2">
-        <v>84</v>
+        <v>496</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>496</v>
+        <v>84</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>84</v>
@@ -10010,16 +10010,16 @@
         <v>84</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AP59" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -10137,13 +10137,13 @@
         <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -10387,13 +10387,13 @@
         <v>84</v>
       </c>
       <c r="AN62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP62" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10511,13 +10511,13 @@
         <v>84</v>
       </c>
       <c r="AN63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP63" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10760,16 +10760,16 @@
         <v>84</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO65" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AP65" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10885,25 +10885,25 @@
         <v>84</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AP66" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="AO66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP66" t="s" s="2">
+      <c r="AQ66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR66" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="AQ66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR66" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="67" hidden="true">
@@ -11016,16 +11016,16 @@
         <v>84</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO67" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AP67" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -11139,25 +11139,25 @@
         <v>84</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="AM68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AP68" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="AO68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP68" t="s" s="2">
+      <c r="AQ68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR68" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR68" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="69" hidden="true">
@@ -11262,25 +11262,25 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>84</v>
+        <v>580</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>580</v>
+        <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO69" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="AO69" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP69" t="s" s="2">
-        <v>84</v>
+        <v>582</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>582</v>
+        <v>84</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>84</v>
@@ -11391,25 +11391,25 @@
         <v>84</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="AN70" t="s" s="2">
+      <c r="AP70" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="AO70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP70" t="s" s="2">
+      <c r="AQ70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR70" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR70" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="71" hidden="true">
@@ -11514,28 +11514,28 @@
         <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>84</v>
+        <v>597</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>597</v>
+        <v>84</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="AN71" t="s" s="2">
+      <c r="AO71" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>600</v>
       </c>
       <c r="AQ71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR71" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AR71" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="72" hidden="true">
@@ -11648,16 +11648,16 @@
         <v>84</v>
       </c>
       <c r="AM72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO72" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="AN72" t="s" s="2">
+      <c r="AP72" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11775,13 +11775,13 @@
         <v>84</v>
       </c>
       <c r="AN73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP73" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
@@ -11901,13 +11901,13 @@
         <v>84</v>
       </c>
       <c r="AN74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -12029,13 +12029,13 @@
         <v>84</v>
       </c>
       <c r="AN75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP75" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
@@ -12150,16 +12150,16 @@
         <v>84</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO76" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AP76" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
@@ -12274,16 +12274,16 @@
         <v>84</v>
       </c>
       <c r="AM77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO77" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="AN77" t="s" s="2">
+      <c r="AP77" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12399,19 +12399,19 @@
         <v>84</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="AM78" t="s" s="2">
+      <c r="AO78" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="AN78" t="s" s="2">
+      <c r="AP78" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
@@ -12527,19 +12527,19 @@
         <v>84</v>
       </c>
       <c r="AL79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="AM79" t="s" s="2">
+      <c r="AO79" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="AN79" t="s" s="2">
+      <c r="AP79" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP79" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
@@ -12659,13 +12659,13 @@
         <v>84</v>
       </c>
       <c r="AN80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP80" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
@@ -12780,16 +12780,16 @@
         <v>84</v>
       </c>
       <c r="AM81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO81" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="AN81" t="s" s="2">
+      <c r="AP81" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
@@ -12906,16 +12906,16 @@
         <v>84</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO82" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="AN82" t="s" s="2">
+      <c r="AP82" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
@@ -13032,16 +13032,16 @@
         <v>84</v>
       </c>
       <c r="AM83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO83" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="AN83" t="s" s="2">
+      <c r="AP83" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -13160,16 +13160,16 @@
         <v>84</v>
       </c>
       <c r="AM84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>674</v>
       </c>
-      <c r="AN84" t="s" s="2">
+      <c r="AP84" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13287,13 +13287,13 @@
         <v>84</v>
       </c>
       <c r="AN85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP85" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -13413,13 +13413,13 @@
         <v>84</v>
       </c>
       <c r="AN86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP86" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP86" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -13541,13 +13541,13 @@
         <v>84</v>
       </c>
       <c r="AN87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP87" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP87" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -13663,22 +13663,22 @@
         <v>84</v>
       </c>
       <c r="AL88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>684</v>
       </c>
-      <c r="AM88" t="s" s="2">
+      <c r="AO88" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AN88" t="s" s="2">
+      <c r="AP88" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AO88" t="s" s="2">
+      <c r="AQ88" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AP88" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ88" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR88" t="s" s="2">
         <v>84</v>
@@ -13791,25 +13791,25 @@
         <v>84</v>
       </c>
       <c r="AL89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>690</v>
       </c>
-      <c r="AM89" t="s" s="2">
+      <c r="AO89" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AN89" t="s" s="2">
+      <c r="AP89" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AO89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP89" t="s" s="2">
+      <c r="AQ89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR89" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AQ89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR89" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="90" hidden="true">
@@ -13922,16 +13922,16 @@
         <v>84</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO90" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN90" t="s" s="2">
+      <c r="AP90" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP90" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
@@ -14047,25 +14047,25 @@
         <v>84</v>
       </c>
       <c r="AL91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="AM91" t="s" s="2">
+      <c r="AO91" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="AN91" t="s" s="2">
+      <c r="AP91" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="AO91" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP91" t="s" s="2">
+      <c r="AQ91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR91" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="AQ91" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR91" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="92" hidden="true">
@@ -14178,16 +14178,16 @@
         <v>84</v>
       </c>
       <c r="AM92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO92" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="AN92" t="s" s="2">
+      <c r="AP92" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -794,7 +794,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
   </si>
   <si>
-    <t>656: transform using #entered-in-error on GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (#120.5-4) case not null</t>
+    <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (#120.5-4) case not null</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -2552,7 +2552,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="117.765625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="118.1171875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="98.75" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3738" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3738" uniqueCount="702">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,7 +120,7 @@
     <t>Abstract</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -1699,6 +1699,9 @@
   <si>
     <t>obs-6
 vs-2</t>
+  </si>
+  <si>
+    <t>1792: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -2186,6 +2189,9 @@
   <si>
     <t>obs-6
 vs-3</t>
+  </si>
+  <si>
+    <t>1793: target not supported</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>
@@ -10754,7 +10760,7 @@
         <v>106</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>84</v>
+        <v>542</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>84</v>
@@ -10769,7 +10775,7 @@
         <v>137</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10780,14 +10786,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10809,16 +10815,16 @@
         <v>183</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -10846,10 +10852,10 @@
         <v>188</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>84</v>
@@ -10867,7 +10873,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10891,27 +10897,27 @@
         <v>84</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR66" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10934,19 +10940,19 @@
         <v>84</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
@@ -10995,7 +11001,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11022,10 +11028,10 @@
         <v>84</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -11036,10 +11042,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11065,13 +11071,13 @@
         <v>183</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -11097,13 +11103,13 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>84</v>
@@ -11121,7 +11127,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11145,27 +11151,27 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11191,16 +11197,16 @@
         <v>183</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -11229,7 +11235,7 @@
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -11247,7 +11253,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11262,7 +11268,7 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>84</v>
@@ -11274,10 +11280,10 @@
         <v>84</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11288,10 +11294,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11314,16 +11320,16 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -11373,7 +11379,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11397,27 +11403,27 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11440,16 +11446,16 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11499,7 +11505,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11514,7 +11520,7 @@
         <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>84</v>
@@ -11523,27 +11529,27 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11566,19 +11572,19 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11627,7 +11633,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11639,7 +11645,7 @@
         <v>84</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>84</v>
@@ -11654,10 +11660,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11668,10 +11674,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11792,10 +11798,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11918,14 +11924,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11947,10 +11953,10 @@
         <v>140</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>143</v>
@@ -12005,7 +12011,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12046,10 +12052,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12072,13 +12078,13 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -12129,7 +12135,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12138,7 +12144,7 @@
         <v>94</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>106</v>
@@ -12156,10 +12162,10 @@
         <v>84</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
@@ -12170,10 +12176,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12196,13 +12202,13 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -12253,7 +12259,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12262,7 +12268,7 @@
         <v>94</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>106</v>
@@ -12280,10 +12286,10 @@
         <v>84</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12294,10 +12300,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12323,16 +12329,16 @@
         <v>183</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12360,10 +12366,10 @@
         <v>118</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
@@ -12381,7 +12387,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12405,13 +12411,13 @@
         <v>84</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
@@ -12422,10 +12428,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12451,16 +12457,16 @@
         <v>183</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -12485,13 +12491,13 @@
         <v>84</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>84</v>
@@ -12509,7 +12515,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12533,13 +12539,13 @@
         <v>84</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
@@ -12550,10 +12556,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12576,17 +12582,17 @@
         <v>84</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
@@ -12635,7 +12641,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12665,7 +12671,7 @@
         <v>84</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
@@ -12676,10 +12682,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12705,10 +12711,10 @@
         <v>161</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12759,7 +12765,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12786,10 +12792,10 @@
         <v>84</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
@@ -12800,10 +12806,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12826,16 +12832,16 @@
         <v>95</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12885,7 +12891,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12912,10 +12918,10 @@
         <v>84</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
@@ -12926,10 +12932,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12952,16 +12958,16 @@
         <v>95</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -13011,7 +13017,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13038,10 +13044,10 @@
         <v>84</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -13052,10 +13058,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13078,19 +13084,19 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>84</v>
@@ -13139,7 +13145,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13151,7 +13157,7 @@
         <v>84</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>84</v>
@@ -13166,10 +13172,10 @@
         <v>84</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13180,10 +13186,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13304,10 +13310,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13430,14 +13436,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -13459,10 +13465,10 @@
         <v>140</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>143</v>
@@ -13517,7 +13523,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13558,10 +13564,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13587,16 +13593,16 @@
         <v>183</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>84</v>
@@ -13645,7 +13651,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>94</v>
@@ -13669,7 +13675,7 @@
         <v>84</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>352</v>
@@ -13686,10 +13692,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13715,13 +13721,13 @@
         <v>430</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="O89" t="s" s="2">
         <v>434</v>
@@ -13773,7 +13779,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13782,7 +13788,7 @@
         <v>94</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>106</v>
@@ -13797,7 +13803,7 @@
         <v>84</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>439</v>
@@ -13814,10 +13820,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13843,13 +13849,13 @@
         <v>183</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>538</v>
@@ -13901,7 +13907,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13910,13 +13916,13 @@
         <v>94</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>84</v>
+        <v>697</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>84</v>
@@ -13931,7 +13937,7 @@
         <v>137</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
@@ -13942,14 +13948,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13971,16 +13977,16 @@
         <v>183</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>84</v>
@@ -14008,10 +14014,10 @@
         <v>188</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>84</v>
@@ -14029,7 +14035,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14053,27 +14059,27 @@
         <v>84</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14099,16 +14105,16 @@
         <v>85</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>84</v>
@@ -14157,7 +14163,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14184,10 +14190,10 @@
         <v>84</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1701,7 +1701,7 @@
 vs-2</t>
   </si>
   <si>
-    <t>1792: target not supported</t>
+    <t>1793: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -2191,7 +2191,7 @@
 vs-3</t>
   </si>
   <si>
-    <t>1793: target not supported</t>
+    <t>1794: target not supported</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (#120.5) to us-core-vital-signs</t>
+    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (120.5) to us-core-vital-signs</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -662,7 +662,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>660: source value from GMRV VITAL MEASUREMENT - IEN (#120.5-.001)</t>
+    <t>660: source value from GMRV VITAL MEASUREMENT - IEN (120.5-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -794,7 +794,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
   </si>
   <si>
-    <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (#120.5-4) case not null</t>
+    <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) case not null</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -1133,7 +1133,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFVitalsCodes</t>
   </si>
   <si>
-    <t>661: terminologyMaps using VF_VitalsCodes on GMRV VITAL MEASUREMENT - VITAL TYPE (#120.5-.03)</t>
+    <t>661: terminologyMaps using VF_VitalsCodes on GMRV VITAL MEASUREMENT - VITAL TYPE (120.5-.03)</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -1158,7 +1158,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>659: reference from GMRV VITAL MEASUREMENT - PATIENT (#120.5-.02)</t>
+    <t>659: reference from GMRV VITAL MEASUREMENT - PATIENT (120.5-.02)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1284,7 +1284,7 @@
 </t>
   </si>
   <si>
-    <t>657: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS TAKEN (#120.5-.01)</t>
+    <t>657: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS TAKEN (120.5-.01)</t>
   </si>
   <si>
     <t>Vital.VitalSign.VitalSignTakenDateTime,Vital.VitalSignQualifier.VitalSignTakenDateTime</t>
@@ -1306,7 +1306,7 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
-    <t>652: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS ENTERED (#120.5-.04)</t>
+    <t>652: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS ENTERED (120.5-.04)</t>
   </si>
   <si>
     <t>Vital.VitalSign.VitalSignEnteredDateTime</t>
@@ -1337,7 +1337,7 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t>1653: reference from GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (#120.5-.05)</t>
+    <t>1653: reference from GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (120.5-.05)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1440,7 +1440,7 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>664: source value from GMRV VITAL MEASUREMENT - RATE (#120.5-1.2) case VUID not = 4500634</t>
+    <t>664: source value from GMRV VITAL MEASUREMENT - RATE (120.5-1.2) case VUID not = 4500634</t>
   </si>
   <si>
     <t>Vital.VitalSign.Diastolic,Vital.VitalSign.Systolic,Vital.VitalSign.VitalResult,Vital.VitalSign.VitalResultNumeric</t>
@@ -1555,7 +1555,7 @@
     <t>Quantity.code</t>
   </si>
   <si>
-    <t>665: transform using VF_VitalsUnits on GMRV VITAL MEASUREMENT - VITAL TYPE (#120.5-.03)</t>
+    <t>665: transform using VF_VitalsUnits on GMRV VITAL MEASUREMENT - VITAL TYPE (120.5-.03)</t>
   </si>
   <si>
     <t>PQ.code, MO.currency, PQ.translation.code</t>
@@ -1821,7 +1821,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFVitalsMethod</t>
   </si>
   <si>
-    <t>867: terminologyMaps using VF_VitalsMethod on GMRV VITAL MEASUREMENT - QUALIFIER (#120.5-5)</t>
+    <t>867: terminologyMaps using VF_VitalsMethod on GMRV VITAL MEASUREMENT - QUALIFIER (120.5-5)</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1874,7 +1874,7 @@
     <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
   </si>
   <si>
-    <t>1655: reference from GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (#120.5-5 &gt; 120.52-99.99)</t>
+    <t>1655: reference from GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
   </si>
   <si>
     <t>&lt; 49062001 |Device|</t>
@@ -2558,7 +2558,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="118.1171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="116.58203125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="98.75" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4133" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4133" uniqueCount="732">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1217,6 +1217,9 @@
     <t>661: terminologyMaps using VF_VitalsCodes on GMRV VITAL MEASUREMENT - VITAL TYPE (120.5-.03)</t>
   </si>
   <si>
+    <t>Vital.VitalSign.VitalTypeIEN</t>
+  </si>
+  <si>
     <t>Observation.code.text</t>
   </si>
   <si>
@@ -1242,6 +1245,9 @@
     <t>659: reference from GMRV VITAL MEASUREMENT - PATIENT (120.5-.02)</t>
   </si>
   <si>
+    <t>Vital.VitalSign.PatientIEN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1419,6 +1425,9 @@
   </si>
   <si>
     <t>1653: reference from GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (120.5-.05)</t>
+  </si>
+  <si>
+    <t>Vital.VitalSign.LocationIEN</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -8180,7 +8189,7 @@
         <v>386</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>84</v>
+        <v>387</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>84</v>
@@ -8203,10 +8212,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8331,10 +8340,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8357,19 +8366,19 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8418,7 +8427,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8433,25 +8442,25 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>84</v>
+        <v>396</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>84</v>
@@ -8459,10 +8468,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8485,16 +8494,16 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8544,7 +8553,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8574,10 +8583,10 @@
         <v>378</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>84</v>
@@ -8585,14 +8594,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8611,19 +8620,19 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8672,7 +8681,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8693,19 +8702,19 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>84</v>
@@ -8713,14 +8722,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -8739,19 +8748,19 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8788,7 +8797,7 @@
         <v>84</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
@@ -8798,7 +8807,7 @@
         <v>143</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8807,10 +8816,10 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>84</v>
@@ -8819,19 +8828,19 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>84</v>
@@ -8839,16 +8848,16 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8867,19 +8876,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8928,7 +8937,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8937,31 +8946,31 @@
         <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>84</v>
@@ -8969,10 +8978,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8995,16 +9004,16 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9054,7 +9063,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9069,10 +9078,10 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>84</v>
@@ -9081,13 +9090,13 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>84</v>
@@ -9095,10 +9104,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9121,17 +9130,17 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -9180,7 +9189,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9195,25 +9204,25 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>84</v>
+        <v>453</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>84</v>
@@ -9221,10 +9230,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9247,19 +9256,19 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -9287,16 +9296,16 @@
         <v>214</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
@@ -9306,7 +9315,7 @@
         <v>143</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9315,7 +9324,7 @@
         <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
@@ -9330,30 +9339,30 @@
         <v>84</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>84</v>
@@ -9375,19 +9384,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9415,10 +9424,10 @@
         <v>214</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9436,7 +9445,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9445,7 +9454,7 @@
         <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>106</v>
@@ -9460,27 +9469,27 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9601,10 +9610,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9727,10 +9736,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9753,19 +9762,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9814,7 +9823,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9829,10 +9838,10 @@
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>84</v>
@@ -9841,10 +9850,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9855,10 +9864,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9884,20 +9893,20 @@
         <v>114</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q58" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="R58" t="s" s="2">
         <v>84</v>
@@ -9921,10 +9930,10 @@
         <v>174</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9942,7 +9951,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9969,10 +9978,10 @@
         <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9983,10 +9992,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10012,14 +10021,14 @@
         <v>196</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -10068,7 +10077,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10095,10 +10104,10 @@
         <v>84</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -10109,10 +10118,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10138,14 +10147,14 @@
         <v>108</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -10194,7 +10203,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10203,7 +10212,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -10221,10 +10230,10 @@
         <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -10235,10 +10244,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10264,16 +10273,16 @@
         <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -10322,7 +10331,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10337,10 +10346,10 @@
         <v>106</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>84</v>
+        <v>387</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>84</v>
@@ -10349,10 +10358,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10363,10 +10372,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10392,10 +10401,10 @@
         <v>196</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10487,10 +10496,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10609,13 +10618,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>84</v>
@@ -10637,16 +10646,16 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10737,10 +10746,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10861,10 +10870,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10985,10 +10994,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11028,7 +11037,7 @@
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>84</v>
@@ -11111,10 +11120,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11137,7 +11146,7 @@
         <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>172</v>
@@ -11155,7 +11164,7 @@
         <v>84</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>84</v>
@@ -11235,10 +11244,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11264,10 +11273,10 @@
         <v>196</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11318,7 +11327,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11359,10 +11368,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11388,16 +11397,16 @@
         <v>171</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11425,10 +11434,10 @@
         <v>214</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11446,7 +11455,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11455,13 +11464,13 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>84</v>
@@ -11476,7 +11485,7 @@
         <v>137</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11487,14 +11496,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11516,16 +11525,16 @@
         <v>171</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11553,10 +11562,10 @@
         <v>214</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11574,7 +11583,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11598,27 +11607,27 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11641,19 +11650,19 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11702,7 +11711,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11729,10 +11738,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11743,10 +11752,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11772,13 +11781,13 @@
         <v>171</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11804,13 +11813,13 @@
         <v>84</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>84</v>
@@ -11828,7 +11837,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11852,27 +11861,27 @@
         <v>84</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11898,16 +11907,16 @@
         <v>171</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
@@ -11936,7 +11945,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -11954,7 +11963,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11969,7 +11978,7 @@
         <v>106</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>84</v>
@@ -11981,10 +11990,10 @@
         <v>84</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -11995,10 +12004,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12021,16 +12030,16 @@
         <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12080,7 +12089,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12104,27 +12113,27 @@
         <v>84</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12147,16 +12156,16 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12206,7 +12215,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12230,27 +12239,27 @@
         <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12273,19 +12282,19 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12334,7 +12343,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12346,7 +12355,7 @@
         <v>84</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>84</v>
@@ -12361,10 +12370,10 @@
         <v>84</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12375,10 +12384,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12499,10 +12508,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12625,14 +12634,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -12654,10 +12663,10 @@
         <v>139</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>183</v>
@@ -12712,7 +12721,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12753,10 +12762,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12779,13 +12788,13 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12836,7 +12845,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12845,7 +12854,7 @@
         <v>94</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>106</v>
@@ -12863,10 +12872,10 @@
         <v>84</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
@@ -12877,10 +12886,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12903,13 +12912,13 @@
         <v>84</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12960,7 +12969,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12969,7 +12978,7 @@
         <v>94</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>106</v>
@@ -12987,10 +12996,10 @@
         <v>84</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
@@ -13001,10 +13010,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13030,16 +13039,16 @@
         <v>171</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>84</v>
@@ -13067,10 +13076,10 @@
         <v>118</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>84</v>
@@ -13088,7 +13097,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13112,13 +13121,13 @@
         <v>84</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -13129,10 +13138,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13158,16 +13167,16 @@
         <v>171</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>84</v>
@@ -13192,13 +13201,13 @@
         <v>84</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>84</v>
@@ -13216,7 +13225,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13240,13 +13249,13 @@
         <v>84</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13257,10 +13266,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13283,17 +13292,17 @@
         <v>84</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>84</v>
@@ -13342,7 +13351,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13372,7 +13381,7 @@
         <v>84</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -13383,10 +13392,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13412,10 +13421,10 @@
         <v>196</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13466,7 +13475,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13493,10 +13502,10 @@
         <v>84</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -13507,10 +13516,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13533,16 +13542,16 @@
         <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13592,7 +13601,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13619,10 +13628,10 @@
         <v>84</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -13633,10 +13642,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13659,16 +13668,16 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13718,7 +13727,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13745,10 +13754,10 @@
         <v>84</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -13759,10 +13768,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13785,19 +13794,19 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
@@ -13846,7 +13855,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13858,7 +13867,7 @@
         <v>84</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>84</v>
@@ -13873,10 +13882,10 @@
         <v>84</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -13887,10 +13896,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14011,10 +14020,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14137,14 +14146,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -14166,10 +14175,10 @@
         <v>139</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>183</v>
@@ -14224,7 +14233,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14265,10 +14274,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14294,16 +14303,16 @@
         <v>171</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14352,7 +14361,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>94</v>
@@ -14376,7 +14385,7 @@
         <v>84</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>378</v>
@@ -14393,10 +14402,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14419,19 +14428,19 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>84</v>
@@ -14459,16 +14468,16 @@
         <v>214</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AC94" s="2"/>
       <c r="AD94" t="s" s="2">
@@ -14478,7 +14487,7 @@
         <v>143</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14487,7 +14496,7 @@
         <v>94</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>106</v>
@@ -14502,30 +14511,30 @@
         <v>84</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>84</v>
@@ -14550,16 +14559,16 @@
         <v>171</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -14587,10 +14596,10 @@
         <v>214</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>84</v>
@@ -14608,7 +14617,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14617,7 +14626,7 @@
         <v>94</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>106</v>
@@ -14632,27 +14641,27 @@
         <v>84</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14773,10 +14782,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14899,10 +14908,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14966,7 +14975,7 @@
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>84</v>
@@ -14999,7 +15008,7 @@
         <v>106</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>84</v>
@@ -15025,10 +15034,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15153,10 +15162,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15182,16 +15191,16 @@
         <v>171</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>84</v>
@@ -15219,10 +15228,10 @@
         <v>214</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>84</v>
@@ -15240,7 +15249,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15249,13 +15258,13 @@
         <v>94</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>84</v>
@@ -15270,7 +15279,7 @@
         <v>137</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
@@ -15281,14 +15290,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -15310,16 +15319,16 @@
         <v>171</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>84</v>
@@ -15347,10 +15356,10 @@
         <v>214</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>84</v>
@@ -15368,7 +15377,7 @@
         <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15392,27 +15401,27 @@
         <v>84</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15438,16 +15447,16 @@
         <v>85</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>84</v>
@@ -15496,7 +15505,7 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15523,10 +15532,10 @@
         <v>84</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="AQ102" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$139</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4133" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5635" uniqueCount="777">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2173,6 +2173,10 @@
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:code}
+</t>
+  </si>
+  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 vs-3:If there is no a value a data absent reason must be present {value.exists() or dataAbsentReason.exists()}</t>
   </si>
@@ -2230,42 +2234,6 @@
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueCodeableConcept.id</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].id</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueCodeableConcept.extension</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].extension</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueCodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].coding</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCuffSize</t>
-  </si>
-  <si>
-    <t>1805: terminologyMaps using VF_VitalsCuffSize on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueCodeableConcept.text</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].text</t>
-  </si>
-  <si>
     <t>Observation.component.dataAbsentReason</t>
   </si>
   <si>
@@ -2296,6 +2264,174 @@
   </si>
   <si>
     <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition</t>
+  </si>
+  <si>
+    <t>va-pre-condition</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.code</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].coding</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsPrecondition</t>
+  </si>
+  <si>
+    <t>1802: terminologyMaps using VF_VitalsPrecondition on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].text</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.interpretation</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.referenceRange</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device</t>
+  </si>
+  <si>
+    <t>va-pre-condition-device</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.code</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsQualifyingDevice</t>
+  </si>
+  <si>
+    <t>1803: terminologyMaps using VF_VitalsQualifyingDevice on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.interpretation</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.referenceRange</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size</t>
+  </si>
+  <si>
+    <t>va-cuff-size</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.code</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCuffSize</t>
+  </si>
+  <si>
+    <t>1805: terminologyMaps using VF_VitalsCuffSize on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.interpretation</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.referenceRange</t>
   </si>
 </sst>
 </file>
@@ -2612,7 +2748,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR102"/>
+  <dimension ref="A1:AR139"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="91.8671875" customWidth="true" bestFit="true"/>
@@ -2640,7 +2776,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.83984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.3125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -2650,7 +2786,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="144.703125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="148.453125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="98.75" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
@@ -13843,16 +13979,14 @@
         <v>84</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>692</v>
+      </c>
+      <c r="AC89" s="2"/>
       <c r="AD89" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="AF89" t="s" s="2">
         <v>687</v>
@@ -13867,7 +14001,7 @@
         <v>84</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>84</v>
@@ -13882,10 +14016,10 @@
         <v>84</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -13896,10 +14030,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14020,10 +14154,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14146,10 +14280,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14274,10 +14408,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14303,16 +14437,16 @@
         <v>171</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14361,7 +14495,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>94</v>
@@ -14385,7 +14519,7 @@
         <v>84</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>378</v>
@@ -14402,10 +14536,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14431,13 +14565,13 @@
         <v>459</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="O94" t="s" s="2">
         <v>463</v>
@@ -14477,17 +14611,19 @@
         <v>84</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AC94" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14496,7 +14632,7 @@
         <v>94</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>106</v>
@@ -14511,7 +14647,7 @@
         <v>84</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>468</v>
@@ -14528,14 +14664,12 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="C95" t="s" s="2">
         <v>711</v>
       </c>
+      <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
         <v>84</v>
       </c>
@@ -14553,22 +14687,22 @@
         <v>84</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>171</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>463</v>
+        <v>557</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -14596,10 +14730,10 @@
         <v>214</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>464</v>
+        <v>558</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>465</v>
+        <v>559</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>84</v>
@@ -14617,7 +14751,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14626,13 +14760,13 @@
         <v>94</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>84</v>
+        <v>716</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>84</v>
@@ -14641,38 +14775,38 @@
         <v>84</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>709</v>
+        <v>84</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>468</v>
+        <v>137</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>469</v>
+        <v>562</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>470</v>
+        <v>84</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>84</v>
+        <v>564</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>84</v>
@@ -14684,16 +14818,20 @@
         <v>84</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>153</v>
+        <v>565</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+        <v>566</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>568</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>84</v>
       </c>
@@ -14717,13 +14855,13 @@
         <v>84</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>84</v>
+        <v>569</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>84</v>
+        <v>570</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>84</v>
@@ -14741,19 +14879,19 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>155</v>
+        <v>717</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>84</v>
@@ -14765,31 +14903,31 @@
         <v>84</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>84</v>
+        <v>571</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>84</v>
+        <v>572</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>157</v>
+        <v>573</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>84</v>
+        <v>574</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -14808,18 +14946,20 @@
         <v>84</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>198</v>
+        <v>719</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>199</v>
+        <v>720</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>625</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>626</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
       </c>
@@ -14855,19 +14995,19 @@
         <v>84</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>160</v>
+        <v>84</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>161</v>
+        <v>718</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -14879,7 +15019,7 @@
         <v>84</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>84</v>
@@ -14894,10 +15034,10 @@
         <v>84</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>84</v>
+        <v>628</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>157</v>
+        <v>629</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
@@ -14908,12 +15048,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="C98" s="2"/>
+        <v>687</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>722</v>
+      </c>
       <c r="D98" t="s" s="2">
         <v>84</v>
       </c>
@@ -14922,7 +15064,7 @@
         <v>82</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>95</v>
@@ -14934,19 +15076,19 @@
         <v>95</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>302</v>
+        <v>622</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>303</v>
+        <v>688</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>304</v>
+        <v>689</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>305</v>
+        <v>690</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>306</v>
+        <v>691</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>84</v>
@@ -14971,11 +15113,13 @@
         <v>84</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y98" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z98" t="s" s="2">
-        <v>718</v>
+        <v>84</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>84</v>
@@ -14993,7 +15137,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>307</v>
+        <v>687</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15005,10 +15149,10 @@
         <v>84</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>106</v>
+        <v>693</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>719</v>
+        <v>84</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>84</v>
@@ -15020,10 +15164,10 @@
         <v>84</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>308</v>
+        <v>694</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>309</v>
+        <v>695</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
@@ -15034,10 +15178,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>721</v>
+        <v>696</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15057,23 +15201,19 @@
         <v>84</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K99" t="s" s="2">
         <v>196</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>361</v>
+        <v>153</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>84</v>
       </c>
@@ -15121,7 +15261,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>365</v>
+        <v>155</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15133,7 +15273,7 @@
         <v>84</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>84</v>
@@ -15148,10 +15288,10 @@
         <v>84</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>366</v>
+        <v>84</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>367</v>
+        <v>157</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
@@ -15162,24 +15302,24 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>722</v>
+        <v>697</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>84</v>
@@ -15188,20 +15328,18 @@
         <v>84</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>723</v>
+        <v>198</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>724</v>
+        <v>199</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>557</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>84</v>
       </c>
@@ -15225,13 +15363,13 @@
         <v>84</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>558</v>
+        <v>84</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>559</v>
+        <v>84</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>84</v>
@@ -15249,22 +15387,22 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>722</v>
+        <v>161</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>726</v>
+        <v>84</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>727</v>
+        <v>84</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>84</v>
@@ -15276,10 +15414,10 @@
         <v>84</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>562</v>
+        <v>157</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
@@ -15290,14 +15428,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>728</v>
+        <v>698</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>564</v>
+        <v>633</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -15310,25 +15448,25 @@
         <v>84</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>565</v>
+        <v>634</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>566</v>
+        <v>635</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>567</v>
+        <v>183</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>568</v>
+        <v>184</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>84</v>
@@ -15353,13 +15491,13 @@
         <v>84</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>569</v>
+        <v>84</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>570</v>
+        <v>84</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>84</v>
@@ -15377,7 +15515,7 @@
         <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>728</v>
+        <v>636</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15389,7 +15527,7 @@
         <v>84</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>84</v>
@@ -15401,27 +15539,27 @@
         <v>84</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>571</v>
+        <v>84</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>572</v>
+        <v>84</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>573</v>
+        <v>137</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>574</v>
+        <v>84</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>729</v>
+        <v>699</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15429,34 +15567,34 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>730</v>
+        <v>700</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>731</v>
+        <v>701</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>625</v>
+        <v>702</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>626</v>
+        <v>703</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>84</v>
@@ -15481,13 +15619,13 @@
         <v>84</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>84</v>
+        <v>374</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>84</v>
@@ -15505,13 +15643,13 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>729</v>
+        <v>699</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>84</v>
@@ -15529,23 +15667,4727 @@
         <v>84</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>84</v>
+        <v>704</v>
       </c>
       <c r="AO102" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AQ102" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AR102" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="P103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AC103" s="2"/>
+      <c r="AD103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AQ103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR103" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="C104" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="D104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="P104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AP104" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AQ104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR104" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR105" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP106" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR106" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y107" s="2"/>
+      <c r="Z107" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AP107" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AQ107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR107" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AQ108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR108" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP109" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AQ109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR109" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="P110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AP110" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AQ110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR110" t="s" s="2">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO111" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="AP102" t="s" s="2">
+      <c r="AP111" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="AQ102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR102" t="s" s="2">
+      <c r="AQ111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR111" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="C112" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="D112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="P112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="AP112" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="AQ112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR112" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
+      <c r="P113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP113" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR113" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O114" s="2"/>
+      <c r="P114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP114" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR114" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="P115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP115" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR115" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="P116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AP116" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AQ116" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AR116" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="P117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AC117" s="2"/>
+      <c r="AD117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AP117" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AQ117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR117" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="D118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="P118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AP118" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AQ118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR118" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" s="2"/>
+      <c r="P119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP119" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR119" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O120" s="2"/>
+      <c r="P120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP120" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR120" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y121" s="2"/>
+      <c r="Z121" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AP121" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AQ121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR121" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AP122" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AQ122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR122" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="P123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP123" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AQ123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR123" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="P124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AO124" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AP124" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AQ124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR124" t="s" s="2">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="P125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO125" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AP125" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AQ125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR125" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="C126" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="D126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="P126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="AP126" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="AQ126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR126" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
+      <c r="P127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP127" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR127" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O128" s="2"/>
+      <c r="P128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP128" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR128" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="P129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP129" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR129" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="P130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="AO130" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AP130" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AQ130" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AR130" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="O131" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="P131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AC131" s="2"/>
+      <c r="AD131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AO131" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AP131" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AQ131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR131" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="C132" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="D132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="P132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AO132" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AP132" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AQ132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR132" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
+      <c r="P133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP133" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR133" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O134" s="2"/>
+      <c r="P134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP134" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR134" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="135" hidden="true">
+      <c r="A135" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O135" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y135" s="2"/>
+      <c r="Z135" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO135" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AP135" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AQ135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR135" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="136" hidden="true">
+      <c r="A136" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O136" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO136" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AP136" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AQ136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR136" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="137" hidden="true">
+      <c r="A137" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="O137" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="P137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO137" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP137" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AQ137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR137" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="138" hidden="true">
+      <c r="A138" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O138" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="P138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN138" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AO138" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AP138" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AQ138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR138" t="s" s="2">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="139" hidden="true">
+      <c r="A139" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="O139" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="P139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q139" s="2"/>
+      <c r="R139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO139" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AP139" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AQ139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR139" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR102">
+  <autoFilter ref="A1:AR139">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15555,7 +20397,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI101">
+  <conditionalFormatting sqref="A2:AI138">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5635" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5635" uniqueCount="784">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -713,10 +713,16 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
     <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>660-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>
@@ -2284,6 +2290,18 @@
     <t>Observation.component:va-pre-condition.code</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="104158-1"/&gt;
+    &lt;display value="Associated precondition - Reported"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>1802-1: fixed value = http://loinc.org#104158-1 Associated precondition - Reported</t>
+  </si>
+  <si>
     <t>Observation.component:va-pre-condition.value[x]</t>
   </si>
   <si>
@@ -2350,6 +2368,9 @@
     <t>Observation.component:va-pre-condition-device.code</t>
   </si>
   <si>
+    <t>1803-1: fixed value = http://loinc.org#104158-1 Associated precondition - Reported</t>
+  </si>
+  <si>
     <t>Observation.component:va-pre-condition-device.value[x]</t>
   </si>
   <si>
@@ -2399,6 +2420,18 @@
   </si>
   <si>
     <t>Observation.component:va-cuff-size.code</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="8358-4"/&gt;
+    &lt;display value="Blood pressure device cuff size"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>1805-1: fixed value = http://loinc.org#8358-4 Blood pressure device cuff size</t>
   </si>
   <si>
     <t>Observation.component:va-cuff-size.value[x]</t>
@@ -5333,7 +5366,7 @@
         <v>94</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>84</v>
@@ -5364,10 +5397,10 @@
         <v>84</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>84</v>
+        <v>224</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>84</v>
@@ -5403,7 +5436,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -5418,7 +5451,7 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>84</v>
+        <v>227</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>84</v>
@@ -5430,10 +5463,10 @@
         <v>84</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>84</v>
@@ -5444,10 +5477,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5473,13 +5506,13 @@
         <v>196</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5493,7 +5526,7 @@
         <v>84</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="U22" t="s" s="2">
         <v>84</v>
@@ -5529,7 +5562,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -5544,7 +5577,7 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>84</v>
@@ -5556,10 +5589,10 @@
         <v>84</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>84</v>
@@ -5570,10 +5603,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5596,13 +5629,13 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5653,7 +5686,7 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5680,10 +5713,10 @@
         <v>84</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>84</v>
@@ -5694,10 +5727,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5720,16 +5753,16 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5779,7 +5812,7 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5806,10 +5839,10 @@
         <v>84</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>84</v>
@@ -5820,14 +5853,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5846,17 +5879,17 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5905,7 +5938,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5926,16 +5959,16 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>84</v>
@@ -5946,14 +5979,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5972,16 +6005,16 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -6031,7 +6064,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -6052,16 +6085,16 @@
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>84</v>
@@ -6072,10 +6105,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6101,16 +6134,16 @@
         <v>114</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -6139,7 +6172,7 @@
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>84</v>
@@ -6157,7 +6190,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>94</v>
@@ -6172,25 +6205,25 @@
         <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>84</v>
@@ -6198,10 +6231,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6227,16 +6260,16 @@
         <v>171</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -6246,7 +6279,7 @@
         <v>84</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>84</v>
@@ -6264,16 +6297,16 @@
         <v>118</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
@@ -6283,7 +6316,7 @@
         <v>143</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -6298,7 +6331,7 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
@@ -6313,10 +6346,10 @@
         <v>84</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>84</v>
@@ -6324,13 +6357,13 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>84</v>
@@ -6355,16 +6388,16 @@
         <v>171</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -6392,10 +6425,10 @@
         <v>118</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>84</v>
@@ -6413,7 +6446,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6443,10 +6476,10 @@
         <v>84</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>84</v>
@@ -6454,10 +6487,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6578,10 +6611,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6704,10 +6737,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6730,19 +6763,19 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6791,7 +6824,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6818,10 +6851,10 @@
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6832,10 +6865,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6956,10 +6989,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -7082,10 +7115,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7111,23 +7144,23 @@
         <v>108</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>84</v>
@@ -7169,7 +7202,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7196,10 +7229,10 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -7210,10 +7243,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7239,13 +7272,13 @@
         <v>196</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -7295,7 +7328,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7322,10 +7355,10 @@
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -7336,10 +7369,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7365,21 +7398,21 @@
         <v>114</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>84</v>
@@ -7421,7 +7454,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -7448,10 +7481,10 @@
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -7462,10 +7495,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7491,14 +7524,14 @@
         <v>196</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -7547,7 +7580,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7574,10 +7607,10 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -7588,10 +7621,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7614,19 +7647,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7675,7 +7708,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7702,10 +7735,10 @@
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7716,10 +7749,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7745,16 +7778,16 @@
         <v>196</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7803,7 +7836,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7830,10 +7863,10 @@
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7844,14 +7877,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7873,16 +7906,16 @@
         <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7910,10 +7943,10 @@
         <v>214</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>84</v>
@@ -7931,7 +7964,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>94</v>
@@ -7952,30 +7985,30 @@
         <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8096,10 +8129,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8222,10 +8255,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8248,19 +8281,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -8289,7 +8322,7 @@
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>84</v>
@@ -8307,7 +8340,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8322,10 +8355,10 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>84</v>
@@ -8334,10 +8367,10 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -8348,10 +8381,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8377,16 +8410,16 @@
         <v>196</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8435,7 +8468,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8462,10 +8495,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -8476,10 +8509,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8502,19 +8535,19 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8563,7 +8596,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8578,25 +8611,25 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>84</v>
@@ -8604,10 +8637,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8630,16 +8663,16 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8689,7 +8722,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8716,13 +8749,13 @@
         <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>84</v>
@@ -8730,14 +8763,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8756,19 +8789,19 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8817,7 +8850,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8838,19 +8871,19 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>84</v>
@@ -8858,14 +8891,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -8884,19 +8917,19 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8933,7 +8966,7 @@
         <v>84</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
@@ -8943,7 +8976,7 @@
         <v>143</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8952,10 +8985,10 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>84</v>
@@ -8964,19 +8997,19 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>84</v>
@@ -8984,16 +9017,16 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -9012,19 +9045,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -9073,7 +9106,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -9082,31 +9115,31 @@
         <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>84</v>
@@ -9114,10 +9147,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9140,16 +9173,16 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9199,7 +9232,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9214,10 +9247,10 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>84</v>
@@ -9226,13 +9259,13 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>84</v>
@@ -9240,10 +9273,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9266,17 +9299,17 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -9325,7 +9358,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9340,25 +9373,25 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>84</v>
@@ -9366,10 +9399,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9392,19 +9425,19 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -9432,16 +9465,16 @@
         <v>214</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
@@ -9451,7 +9484,7 @@
         <v>143</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9460,7 +9493,7 @@
         <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
@@ -9475,30 +9508,30 @@
         <v>84</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>84</v>
@@ -9520,19 +9553,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9560,10 +9593,10 @@
         <v>214</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9581,7 +9614,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9590,7 +9623,7 @@
         <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>106</v>
@@ -9605,27 +9638,27 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9746,10 +9779,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9872,10 +9905,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9898,19 +9931,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9959,7 +9992,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9974,10 +10007,10 @@
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>84</v>
@@ -9986,10 +10019,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -10000,10 +10033,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10029,20 +10062,20 @@
         <v>114</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q58" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="R58" t="s" s="2">
         <v>84</v>
@@ -10066,10 +10099,10 @@
         <v>174</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -10087,7 +10120,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -10114,10 +10147,10 @@
         <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -10128,10 +10161,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10157,14 +10190,14 @@
         <v>196</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -10213,7 +10246,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10240,10 +10273,10 @@
         <v>84</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -10254,10 +10287,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10283,14 +10316,14 @@
         <v>108</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -10339,7 +10372,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10348,7 +10381,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -10366,10 +10399,10 @@
         <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -10380,10 +10413,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10409,16 +10442,16 @@
         <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -10467,7 +10500,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10482,10 +10515,10 @@
         <v>106</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>84</v>
@@ -10494,10 +10527,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10508,10 +10541,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10537,10 +10570,10 @@
         <v>196</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10632,10 +10665,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10754,13 +10787,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>84</v>
@@ -10782,16 +10815,16 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10882,10 +10915,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11006,10 +11039,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11130,10 +11163,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11173,7 +11206,7 @@
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>84</v>
@@ -11256,10 +11289,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11282,7 +11315,7 @@
         <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>172</v>
@@ -11300,7 +11333,7 @@
         <v>84</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>84</v>
@@ -11380,10 +11413,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11409,10 +11442,10 @@
         <v>196</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11463,7 +11496,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11504,10 +11537,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11533,16 +11566,16 @@
         <v>171</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11570,10 +11603,10 @@
         <v>214</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11591,7 +11624,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11600,13 +11633,13 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>84</v>
@@ -11621,7 +11654,7 @@
         <v>137</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11632,14 +11665,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11661,16 +11694,16 @@
         <v>171</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11698,10 +11731,10 @@
         <v>214</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11719,7 +11752,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11743,27 +11776,27 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11786,19 +11819,19 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11847,7 +11880,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11874,10 +11907,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11888,10 +11921,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11917,13 +11950,13 @@
         <v>171</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11949,13 +11982,13 @@
         <v>84</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>84</v>
@@ -11973,7 +12006,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11997,27 +12030,27 @@
         <v>84</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12043,16 +12076,16 @@
         <v>171</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
@@ -12081,7 +12114,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -12099,7 +12132,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12114,7 +12147,7 @@
         <v>106</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>84</v>
@@ -12126,10 +12159,10 @@
         <v>84</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -12140,10 +12173,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12166,16 +12199,16 @@
         <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12225,7 +12258,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12249,27 +12282,27 @@
         <v>84</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12292,16 +12325,16 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12351,7 +12384,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12375,27 +12408,27 @@
         <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12418,19 +12451,19 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12479,7 +12512,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12491,7 +12524,7 @@
         <v>84</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>84</v>
@@ -12506,10 +12539,10 @@
         <v>84</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12520,10 +12553,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12644,10 +12677,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12770,14 +12803,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -12799,10 +12832,10 @@
         <v>139</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>183</v>
@@ -12857,7 +12890,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12898,10 +12931,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12924,13 +12957,13 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12981,7 +13014,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12990,7 +13023,7 @@
         <v>94</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>106</v>
@@ -13008,10 +13041,10 @@
         <v>84</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
@@ -13022,10 +13055,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13048,13 +13081,13 @@
         <v>84</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -13105,7 +13138,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13114,7 +13147,7 @@
         <v>94</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>106</v>
@@ -13132,10 +13165,10 @@
         <v>84</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
@@ -13146,10 +13179,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13175,16 +13208,16 @@
         <v>171</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>84</v>
@@ -13212,10 +13245,10 @@
         <v>118</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>84</v>
@@ -13233,7 +13266,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13257,13 +13290,13 @@
         <v>84</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -13274,10 +13307,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13303,16 +13336,16 @@
         <v>171</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>84</v>
@@ -13337,13 +13370,13 @@
         <v>84</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>84</v>
@@ -13361,7 +13394,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13385,13 +13418,13 @@
         <v>84</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13402,10 +13435,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13428,17 +13461,17 @@
         <v>84</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>84</v>
@@ -13487,7 +13520,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13517,7 +13550,7 @@
         <v>84</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -13528,10 +13561,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13557,10 +13590,10 @@
         <v>196</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13611,7 +13644,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13638,10 +13671,10 @@
         <v>84</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -13652,10 +13685,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13678,16 +13711,16 @@
         <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13737,7 +13770,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13764,10 +13797,10 @@
         <v>84</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -13778,10 +13811,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13804,16 +13837,16 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13863,7 +13896,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13890,10 +13923,10 @@
         <v>84</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -13904,10 +13937,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13930,19 +13963,19 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
@@ -13979,7 +14012,7 @@
         <v>84</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AC89" s="2"/>
       <c r="AD89" t="s" s="2">
@@ -13989,7 +14022,7 @@
         <v>143</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14001,7 +14034,7 @@
         <v>84</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>84</v>
@@ -14016,10 +14049,10 @@
         <v>84</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -14030,10 +14063,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14154,10 +14187,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14280,14 +14313,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -14309,10 +14342,10 @@
         <v>139</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>183</v>
@@ -14367,7 +14400,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14408,10 +14441,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14437,16 +14470,16 @@
         <v>171</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14474,10 +14507,10 @@
         <v>214</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>84</v>
@@ -14495,7 +14528,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>94</v>
@@ -14519,16 +14552,16 @@
         <v>84</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AR93" t="s" s="2">
         <v>84</v>
@@ -14536,10 +14569,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14562,19 +14595,19 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>84</v>
@@ -14602,10 +14635,10 @@
         <v>214</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>84</v>
@@ -14623,7 +14656,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14632,7 +14665,7 @@
         <v>94</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>106</v>
@@ -14647,27 +14680,27 @@
         <v>84</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14693,16 +14726,16 @@
         <v>171</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -14730,10 +14763,10 @@
         <v>214</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>84</v>
@@ -14751,7 +14784,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14760,13 +14793,13 @@
         <v>94</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>84</v>
@@ -14781,7 +14814,7 @@
         <v>137</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
@@ -14792,14 +14825,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -14821,16 +14854,16 @@
         <v>171</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>84</v>
@@ -14858,10 +14891,10 @@
         <v>214</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>84</v>
@@ -14879,7 +14912,7 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14903,27 +14936,27 @@
         <v>84</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14949,16 +14982,16 @@
         <v>85</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
@@ -15007,7 +15040,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -15034,10 +15067,10 @@
         <v>84</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
@@ -15048,13 +15081,13 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>84</v>
@@ -15076,19 +15109,19 @@
         <v>95</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>84</v>
@@ -15137,7 +15170,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15149,7 +15182,7 @@
         <v>84</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>84</v>
@@ -15164,10 +15197,10 @@
         <v>84</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
@@ -15178,10 +15211,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15302,10 +15335,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15428,14 +15461,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -15457,10 +15490,10 @@
         <v>139</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>183</v>
@@ -15515,7 +15548,7 @@
         <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15556,10 +15589,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15585,16 +15618,16 @@
         <v>171</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>84</v>
@@ -15604,7 +15637,7 @@
         <v>84</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>84</v>
+        <v>729</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>84</v>
@@ -15622,10 +15655,10 @@
         <v>214</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>84</v>
@@ -15643,7 +15676,7 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>94</v>
@@ -15658,7 +15691,7 @@
         <v>106</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>84</v>
+        <v>730</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>84</v>
@@ -15667,16 +15700,16 @@
         <v>84</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>84</v>
@@ -15684,10 +15717,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15710,19 +15743,19 @@
         <v>95</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>84</v>
@@ -15750,16 +15783,16 @@
         <v>214</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
@@ -15769,7 +15802,7 @@
         <v>143</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15778,7 +15811,7 @@
         <v>94</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>106</v>
@@ -15793,30 +15826,30 @@
         <v>84</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR103" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>84</v>
@@ -15841,16 +15874,16 @@
         <v>171</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>84</v>
@@ -15878,10 +15911,10 @@
         <v>214</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>84</v>
@@ -15899,7 +15932,7 @@
         <v>84</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15908,7 +15941,7 @@
         <v>94</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>106</v>
@@ -15923,27 +15956,27 @@
         <v>84</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AQ104" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR104" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16064,10 +16097,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16190,10 +16223,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16216,19 +16249,19 @@
         <v>95</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>84</v>
@@ -16257,7 +16290,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>84</v>
@@ -16275,7 +16308,7 @@
         <v>84</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>82</v>
@@ -16290,7 +16323,7 @@
         <v>106</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>84</v>
@@ -16302,10 +16335,10 @@
         <v>84</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AQ107" t="s" s="2">
         <v>84</v>
@@ -16316,10 +16349,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16345,16 +16378,16 @@
         <v>196</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>84</v>
@@ -16403,7 +16436,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16430,10 +16463,10 @@
         <v>84</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
@@ -16444,10 +16477,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16473,16 +16506,16 @@
         <v>171</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>84</v>
@@ -16510,10 +16543,10 @@
         <v>214</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>84</v>
@@ -16531,7 +16564,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>82</v>
@@ -16540,7 +16573,7 @@
         <v>94</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>106</v>
@@ -16561,7 +16594,7 @@
         <v>137</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>84</v>
@@ -16572,14 +16605,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -16601,16 +16634,16 @@
         <v>171</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>84</v>
@@ -16638,10 +16671,10 @@
         <v>214</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>84</v>
@@ -16659,7 +16692,7 @@
         <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
@@ -16683,27 +16716,27 @@
         <v>84</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR110" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16729,16 +16762,16 @@
         <v>85</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>84</v>
@@ -16787,7 +16820,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -16814,10 +16847,10 @@
         <v>84</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>84</v>
@@ -16828,13 +16861,13 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>84</v>
@@ -16856,19 +16889,19 @@
         <v>95</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>84</v>
@@ -16917,7 +16950,7 @@
         <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>82</v>
@@ -16929,7 +16962,7 @@
         <v>84</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>84</v>
@@ -16944,10 +16977,10 @@
         <v>84</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>84</v>
@@ -16958,10 +16991,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17082,10 +17115,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17208,14 +17241,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -17237,10 +17270,10 @@
         <v>139</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="N115" t="s" s="2">
         <v>183</v>
@@ -17295,7 +17328,7 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
@@ -17336,10 +17369,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17365,16 +17398,16 @@
         <v>171</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>84</v>
@@ -17384,7 +17417,7 @@
         <v>84</v>
       </c>
       <c r="S116" t="s" s="2">
-        <v>84</v>
+        <v>729</v>
       </c>
       <c r="T116" t="s" s="2">
         <v>84</v>
@@ -17402,10 +17435,10 @@
         <v>214</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>84</v>
@@ -17423,7 +17456,7 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>94</v>
@@ -17438,7 +17471,7 @@
         <v>106</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>84</v>
+        <v>753</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>84</v>
@@ -17447,16 +17480,16 @@
         <v>84</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AQ116" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AR116" t="s" s="2">
         <v>84</v>
@@ -17464,10 +17497,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17490,19 +17523,19 @@
         <v>95</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>84</v>
@@ -17530,16 +17563,16 @@
         <v>214</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AC117" s="2"/>
       <c r="AD117" t="s" s="2">
@@ -17549,7 +17582,7 @@
         <v>143</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>82</v>
@@ -17558,7 +17591,7 @@
         <v>94</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>106</v>
@@ -17573,30 +17606,30 @@
         <v>84</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AQ117" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR117" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>84</v>
@@ -17621,16 +17654,16 @@
         <v>171</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>84</v>
@@ -17658,10 +17691,10 @@
         <v>214</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>84</v>
@@ -17679,7 +17712,7 @@
         <v>84</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>82</v>
@@ -17688,7 +17721,7 @@
         <v>94</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>106</v>
@@ -17703,27 +17736,27 @@
         <v>84</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AQ118" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR118" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17844,10 +17877,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17970,10 +18003,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17996,19 +18029,19 @@
         <v>95</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>84</v>
@@ -18037,7 +18070,7 @@
       </c>
       <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>84</v>
@@ -18055,7 +18088,7 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>82</v>
@@ -18070,7 +18103,7 @@
         <v>106</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>84</v>
@@ -18082,10 +18115,10 @@
         <v>84</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AQ121" t="s" s="2">
         <v>84</v>
@@ -18096,10 +18129,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18125,16 +18158,16 @@
         <v>196</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>84</v>
@@ -18183,7 +18216,7 @@
         <v>84</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>82</v>
@@ -18210,10 +18243,10 @@
         <v>84</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>84</v>
@@ -18224,10 +18257,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18253,16 +18286,16 @@
         <v>171</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>84</v>
@@ -18290,10 +18323,10 @@
         <v>214</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>84</v>
@@ -18311,7 +18344,7 @@
         <v>84</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>82</v>
@@ -18320,7 +18353,7 @@
         <v>94</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>106</v>
@@ -18341,7 +18374,7 @@
         <v>137</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AQ123" t="s" s="2">
         <v>84</v>
@@ -18352,14 +18385,14 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -18381,16 +18414,16 @@
         <v>171</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>84</v>
@@ -18418,10 +18451,10 @@
         <v>214</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>84</v>
@@ -18439,7 +18472,7 @@
         <v>84</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>82</v>
@@ -18463,27 +18496,27 @@
         <v>84</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AQ124" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR124" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18509,16 +18542,16 @@
         <v>85</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>84</v>
@@ -18567,7 +18600,7 @@
         <v>84</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>82</v>
@@ -18594,10 +18627,10 @@
         <v>84</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AQ125" t="s" s="2">
         <v>84</v>
@@ -18608,13 +18641,13 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>84</v>
@@ -18636,19 +18669,19 @@
         <v>95</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>84</v>
@@ -18697,7 +18730,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -18709,7 +18742,7 @@
         <v>84</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>84</v>
@@ -18724,10 +18757,10 @@
         <v>84</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>84</v>
@@ -18738,10 +18771,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18862,10 +18895,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18988,14 +19021,14 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -19017,10 +19050,10 @@
         <v>139</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="N129" t="s" s="2">
         <v>183</v>
@@ -19075,7 +19108,7 @@
         <v>84</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19116,10 +19149,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19145,16 +19178,16 @@
         <v>171</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>84</v>
@@ -19164,7 +19197,7 @@
         <v>84</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>84</v>
+        <v>771</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>84</v>
@@ -19182,10 +19215,10 @@
         <v>214</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>84</v>
@@ -19203,7 +19236,7 @@
         <v>84</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>94</v>
@@ -19218,7 +19251,7 @@
         <v>106</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>84</v>
+        <v>772</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>84</v>
@@ -19227,16 +19260,16 @@
         <v>84</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AQ130" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AR130" t="s" s="2">
         <v>84</v>
@@ -19244,10 +19277,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19270,19 +19303,19 @@
         <v>95</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>84</v>
@@ -19310,16 +19343,16 @@
         <v>214</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AC131" s="2"/>
       <c r="AD131" t="s" s="2">
@@ -19329,7 +19362,7 @@
         <v>143</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>82</v>
@@ -19338,7 +19371,7 @@
         <v>94</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>106</v>
@@ -19353,30 +19386,30 @@
         <v>84</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AQ131" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR131" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="D132" t="s" s="2">
         <v>84</v>
@@ -19401,16 +19434,16 @@
         <v>171</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>84</v>
@@ -19438,10 +19471,10 @@
         <v>214</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>84</v>
@@ -19459,7 +19492,7 @@
         <v>84</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>82</v>
@@ -19468,7 +19501,7 @@
         <v>94</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>106</v>
@@ -19483,27 +19516,27 @@
         <v>84</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AQ132" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR132" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19624,10 +19657,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19750,10 +19783,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19776,19 +19809,19 @@
         <v>95</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>84</v>
@@ -19817,7 +19850,7 @@
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>84</v>
@@ -19835,7 +19868,7 @@
         <v>84</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>82</v>
@@ -19850,7 +19883,7 @@
         <v>106</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>84</v>
@@ -19862,10 +19895,10 @@
         <v>84</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AP135" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AQ135" t="s" s="2">
         <v>84</v>
@@ -19876,10 +19909,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19905,16 +19938,16 @@
         <v>196</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>84</v>
@@ -19963,7 +19996,7 @@
         <v>84</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>82</v>
@@ -19990,10 +20023,10 @@
         <v>84</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AP136" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AQ136" t="s" s="2">
         <v>84</v>
@@ -20004,10 +20037,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20033,16 +20066,16 @@
         <v>171</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>84</v>
@@ -20070,10 +20103,10 @@
         <v>214</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>84</v>
@@ -20091,7 +20124,7 @@
         <v>84</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>82</v>
@@ -20100,7 +20133,7 @@
         <v>94</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="AJ137" t="s" s="2">
         <v>106</v>
@@ -20121,7 +20154,7 @@
         <v>137</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AQ137" t="s" s="2">
         <v>84</v>
@@ -20132,14 +20165,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -20161,16 +20194,16 @@
         <v>171</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>84</v>
@@ -20198,10 +20231,10 @@
         <v>214</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>84</v>
@@ -20219,7 +20252,7 @@
         <v>84</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>82</v>
@@ -20243,27 +20276,27 @@
         <v>84</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AP138" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AQ138" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR138" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20289,16 +20322,16 @@
         <v>85</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>84</v>
@@ -20347,7 +20380,7 @@
         <v>84</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>82</v>
@@ -20374,10 +20407,10 @@
         <v>84</v>
       </c>
       <c r="AO139" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AQ139" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -713,7 +713,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/120.5</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -722,7 +722,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>660-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>660-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/120.5</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -713,7 +713,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/120.5</t>
+    <t>http://va.gov/identifiers/$Sta3n/120.5</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -722,7 +722,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>660-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/120.5</t>
+    <t>660-1: fixed value = http://va.gov/identifiers/$Sta3n/120.5</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,7 +120,7 @@
     <t>Abstract</t>
   </si>
   <si>
-    <t>true</t>
+    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
